--- a/BOM/Client-BOM-IoT-Speaker.xlsx
+++ b/BOM/Client-BOM-IoT-Speaker.xlsx
@@ -9,21 +9,18 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="5 Boards" sheetId="1" r:id="rId1"/>
     <sheet name="2 Boards" sheetId="2" r:id="rId2"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId3"/>
-  </externalReferences>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="342">
   <si>
     <t>Component list</t>
   </si>
@@ -850,12 +847,6 @@
     <t>Quantity (2 Boards)</t>
   </si>
   <si>
-    <t>C1, C5, C37, C50, C52, C61, C66, C68</t>
-  </si>
-  <si>
-    <t>C2, C3, C4, C6, C8, C9, C12, C13, C15, C17, C18, C19, C20, C21, C22, C24, C29, C30, C32, C34, C38, C40, C41, C43, C46, C62, C77, C81</t>
-  </si>
-  <si>
     <t>C7, C59</t>
   </si>
   <si>
@@ -892,39 +883,9 @@
     <t>C76</t>
   </si>
   <si>
-    <t>D3, D5, D8</t>
-  </si>
-  <si>
-    <t>FB1, FB2, FB7</t>
-  </si>
-  <si>
-    <t>FB3, FB4, FB5, FB6</t>
-  </si>
-  <si>
-    <t>P1, P2, P3, P5, P6, P7, P8, P9, P10, P11, P12, P13, P14, P15</t>
-  </si>
-  <si>
-    <t>Q2, Q4</t>
-  </si>
-  <si>
-    <t>R1</t>
-  </si>
-  <si>
-    <t>RES SMD 470K OHM 5% 1/10W 0603</t>
-  </si>
-  <si>
-    <t>RES-0603</t>
-  </si>
-  <si>
-    <t>AC0603JR-07470KL</t>
-  </si>
-  <si>
     <t>R3, R7, R12, R42</t>
   </si>
   <si>
-    <t>R4, R8, R13, R17, R18, R20, R24, R25, R26, R27, R46, R47, R54</t>
-  </si>
-  <si>
     <t>R9</t>
   </si>
   <si>
@@ -955,9 +916,6 @@
     <t>R43, R45</t>
   </si>
   <si>
-    <t>R44, R52</t>
-  </si>
-  <si>
     <t>R48, R49, R50, R51</t>
   </si>
   <si>
@@ -994,21 +952,6 @@
     <t>MaxLinear</t>
   </si>
   <si>
-    <t>U10</t>
-  </si>
-  <si>
-    <t>IC OR CTRLR SRC SELECT TSOT23-6</t>
-  </si>
-  <si>
-    <t>SOT-23-6</t>
-  </si>
-  <si>
-    <t>LTC4412IS6#TRPBF</t>
-  </si>
-  <si>
-    <t>Analog Devices / Linear Technology</t>
-  </si>
-  <si>
     <t>Battery</t>
   </si>
   <si>
@@ -1027,19 +970,82 @@
     <t>100pF</t>
   </si>
   <si>
-    <t>470K</t>
-  </si>
-  <si>
-    <t>Quantity per Board</t>
-  </si>
-  <si>
-    <t>Quantity Per Board</t>
-  </si>
-  <si>
-    <t>DZ254R-11-02-63</t>
-  </si>
-  <si>
-    <t>0402N330K250CT</t>
+    <t>C1, C5, C50, C52, C61, C66, C68</t>
+  </si>
+  <si>
+    <t>C2, C3, C4, C6, C8, C12, C13, C62, C77, C81</t>
+  </si>
+  <si>
+    <t>CAP CER 0.1UF 50V X5R 0603</t>
+  </si>
+  <si>
+    <t>CC0603KRX5R9BB104</t>
+  </si>
+  <si>
+    <t>C9, C15, C17, C18, C19, C20, C21, C22, C24, C29, C30, C32, C34, C38, C40, C41, C43, C46</t>
+  </si>
+  <si>
+    <t>GRM1555C1E330JA01D</t>
+  </si>
+  <si>
+    <t>C37</t>
+  </si>
+  <si>
+    <t>CAP CER 10UF 10V X5R 0603</t>
+  </si>
+  <si>
+    <t>CC0603KRX5R6BB106</t>
+  </si>
+  <si>
+    <t>D3, D5</t>
+  </si>
+  <si>
+    <t>FB1, FB2, FB3</t>
+  </si>
+  <si>
+    <t>FB4, FB5, FB6, FB7</t>
+  </si>
+  <si>
+    <t>P1, P2, P3, P4, P5, P6, P7, P8, P9, P10, P11, P12, P13, P14, P15</t>
+  </si>
+  <si>
+    <t>Q2, Q3, Q4</t>
+  </si>
+  <si>
+    <t>R1, R4, R8, R13, R17, R18, R20, R24, R25, R26, R27, R46, R47, R54</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>RES SMD 3.3K OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>RC0603FR-073K3L</t>
+  </si>
+  <si>
+    <t>Yageo Phycomp</t>
+  </si>
+  <si>
+    <t>R5, R44, R52</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>RES 100K OHM 5% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>RC0603JR-07100KL</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>3.3K</t>
+  </si>
+  <si>
+    <t>100K</t>
   </si>
 </sst>
 </file>
@@ -1238,7 +1244,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1457,11 +1463,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1592,9 +1613,6 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1628,30 +1646,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1664,10 +1665,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1799,25 +1809,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="9">
-          <cell r="B9" t="str">
-            <v>#</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2084,7 +2075,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L80"/>
+  <dimension ref="A1:L82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -2109,10 +2100,10 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="71"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="65"/>
     </row>
     <row r="2" spans="1:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2122,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="11"/>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="51" t="s">
         <v>267</v>
       </c>
       <c r="G2" s="12"/>
@@ -2140,7 +2131,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="13"/>
-      <c r="F3" s="53" t="s">
+      <c r="F3" s="52" t="s">
         <v>268</v>
       </c>
       <c r="G3" s="13"/>
@@ -2148,7 +2139,7 @@
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
-      <c r="L3" s="72"/>
+      <c r="L3" s="66"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2158,7 +2149,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="13"/>
-      <c r="F4" s="53" t="s">
+      <c r="F4" s="52" t="s">
         <v>268</v>
       </c>
       <c r="G4" s="14"/>
@@ -2166,7 +2157,7 @@
       <c r="I4" s="7"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
-      <c r="L4" s="73"/>
+      <c r="L4" s="67"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2176,7 +2167,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="13"/>
-      <c r="F5" s="54" t="s">
+      <c r="F5" s="53" t="s">
         <v>5</v>
       </c>
       <c r="G5" s="15"/>
@@ -2184,7 +2175,7 @@
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
-      <c r="L5" s="73"/>
+      <c r="L5" s="67"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2198,7 +2189,7 @@
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
-      <c r="L6" s="73"/>
+      <c r="L6" s="67"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2212,7 +2203,7 @@
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
-      <c r="L7" s="73"/>
+      <c r="L7" s="67"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2226,7 +2217,7 @@
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
-      <c r="L8" s="73"/>
+      <c r="L8" s="67"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2255,7 +2246,7 @@
         <v>271</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="K9" s="30" t="s">
         <v>272</v>
@@ -2267,14 +2258,14 @@
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="45">
-        <f t="shared" ref="B10:B19" si="0">ROW(B10) - ROW($B$9)</f>
+        <f t="shared" ref="B10:B21" si="0">ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
       <c r="C10" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="74" t="s">
-        <v>275</v>
+      <c r="D10" s="62" t="s">
+        <v>316</v>
       </c>
       <c r="E10" s="47" t="s">
         <v>60</v>
@@ -2292,47 +2283,47 @@
         <v>242</v>
       </c>
       <c r="J10" s="37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K10" s="37">
         <f>J10*5</f>
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="L10" s="46"/>
     </row>
-    <row r="11" spans="1:12" ht="48" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="45">
-        <f>ROW(B11) - ROW($B$9)</f>
+      <c r="B11" s="44">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C11" s="49" t="s">
+      <c r="C11" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="75" t="s">
-        <v>276</v>
-      </c>
-      <c r="E11" s="47" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11" s="47" t="s">
-        <v>122</v>
-      </c>
-      <c r="G11" s="47" t="s">
-        <v>156</v>
-      </c>
-      <c r="H11" s="47" t="s">
+      <c r="D11" s="63" t="s">
+        <v>317</v>
+      </c>
+      <c r="E11" s="37" t="s">
+        <v>318</v>
+      </c>
+      <c r="F11" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="G11" s="37" t="s">
+        <v>319</v>
+      </c>
+      <c r="H11" s="37" t="s">
         <v>205</v>
       </c>
-      <c r="I11" s="47" t="s">
+      <c r="I11" s="37" t="s">
         <v>241</v>
       </c>
       <c r="J11" s="47">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="K11" s="37">
-        <f>J11*5</f>
-        <v>140</v>
+        <f t="shared" ref="K11:K74" si="1">J11*5</f>
+        <v>50</v>
       </c>
       <c r="L11" s="47"/>
     </row>
@@ -2345,8 +2336,8 @@
       <c r="C12" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="74" t="s">
-        <v>277</v>
+      <c r="D12" s="62" t="s">
+        <v>275</v>
       </c>
       <c r="E12" s="37" t="s">
         <v>58</v>
@@ -2367,84 +2358,84 @@
         <v>2</v>
       </c>
       <c r="K12" s="37">
-        <f t="shared" ref="K12:K75" si="1">J12*5</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L12" s="55"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L12" s="54"/>
+    </row>
+    <row r="13" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="44">
+      <c r="B13" s="45">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="48" t="s">
+      <c r="C13" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="74" t="s">
-        <v>278</v>
-      </c>
-      <c r="E13" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="F13" s="37" t="s">
-        <v>269</v>
-      </c>
-      <c r="G13" s="37" t="s">
-        <v>123</v>
-      </c>
-      <c r="H13" s="37" t="s">
-        <v>206</v>
-      </c>
-      <c r="I13" s="37" t="s">
-        <v>243</v>
-      </c>
-      <c r="J13" s="37">
-        <v>2</v>
+      <c r="D13" s="63" t="s">
+        <v>320</v>
+      </c>
+      <c r="E13" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G13" s="47" t="s">
+        <v>156</v>
+      </c>
+      <c r="H13" s="47" t="s">
+        <v>205</v>
+      </c>
+      <c r="I13" s="47" t="s">
+        <v>241</v>
+      </c>
+      <c r="J13" s="47">
+        <v>18</v>
       </c>
       <c r="K13" s="37">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L13" s="55"/>
-    </row>
-    <row r="14" spans="1:12" ht="48" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="L13" s="54"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="45">
+      <c r="B14" s="44">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C14" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="75" t="s">
-        <v>279</v>
-      </c>
-      <c r="E14" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="F14" s="47" t="s">
-        <v>119</v>
-      </c>
-      <c r="G14" s="47" t="s">
-        <v>154</v>
-      </c>
-      <c r="H14" s="47" t="s">
-        <v>205</v>
-      </c>
-      <c r="I14" s="47" t="s">
-        <v>240</v>
-      </c>
-      <c r="J14" s="47">
-        <v>22</v>
+      <c r="D14" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="E14" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>269</v>
+      </c>
+      <c r="G14" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="H14" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="I14" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="J14" s="37">
+        <v>2</v>
       </c>
       <c r="K14" s="37">
         <f t="shared" si="1"/>
-        <v>110</v>
-      </c>
-      <c r="L14" s="55"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="L14" s="54"/>
+    </row>
+    <row r="15" spans="1:12" ht="48" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="45">
         <f t="shared" si="0"/>
@@ -2453,32 +2444,32 @@
       <c r="C15" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="74" t="s">
-        <v>280</v>
+      <c r="D15" s="63" t="s">
+        <v>277</v>
       </c>
       <c r="E15" s="47" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F15" s="47" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="G15" s="47" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H15" s="47" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I15" s="47" t="s">
-        <v>243</v>
-      </c>
-      <c r="J15" s="37">
-        <v>1</v>
+        <v>240</v>
+      </c>
+      <c r="J15" s="47">
+        <v>22</v>
       </c>
       <c r="K15" s="37">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L15" s="55"/>
+        <v>110</v>
+      </c>
+      <c r="L15" s="54"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
@@ -2489,68 +2480,68 @@
       <c r="C16" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="75" t="s">
-        <v>281</v>
+      <c r="D16" s="62" t="s">
+        <v>278</v>
       </c>
       <c r="E16" s="47" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F16" s="47" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G16" s="47" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H16" s="47" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I16" s="47" t="s">
-        <v>244</v>
-      </c>
-      <c r="J16" s="47">
-        <v>6</v>
+        <v>243</v>
+      </c>
+      <c r="J16" s="37">
+        <v>1</v>
       </c>
       <c r="K16" s="37">
         <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="L16" s="55"/>
+        <v>5</v>
+      </c>
+      <c r="L16" s="54"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="44">
+      <c r="B17" s="45">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C17" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="74" t="s">
-        <v>282</v>
-      </c>
-      <c r="E17" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="F17" s="37" t="s">
-        <v>122</v>
-      </c>
-      <c r="G17" s="37" t="s">
-        <v>338</v>
-      </c>
-      <c r="H17" s="37" t="s">
-        <v>208</v>
-      </c>
-      <c r="I17" s="37" t="s">
-        <v>245</v>
-      </c>
-      <c r="J17" s="37">
-        <v>3</v>
+      <c r="D17" s="63" t="s">
+        <v>279</v>
+      </c>
+      <c r="E17" s="47" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="G17" s="47" t="s">
+        <v>158</v>
+      </c>
+      <c r="H17" s="47" t="s">
+        <v>205</v>
+      </c>
+      <c r="I17" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="J17" s="47">
+        <v>6</v>
       </c>
       <c r="K17" s="37">
         <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="L17" s="55"/>
+        <v>30</v>
+      </c>
+      <c r="L17" s="54"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
@@ -2561,23 +2552,23 @@
       <c r="C18" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="74" t="s">
-        <v>283</v>
+      <c r="D18" s="62" t="s">
+        <v>280</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>119</v>
-      </c>
-      <c r="G18" s="37" t="s">
-        <v>152</v>
+        <v>122</v>
+      </c>
+      <c r="G18" s="55" t="s">
+        <v>321</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="J18" s="37">
         <v>3</v>
@@ -2586,218 +2577,218 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="L18" s="55"/>
+      <c r="L18" s="54"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="44">
+      <c r="B19" s="45">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C19" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="75" t="s">
-        <v>284</v>
-      </c>
-      <c r="E19" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="F19" s="37" t="s">
+      <c r="D19" s="63" t="s">
+        <v>322</v>
+      </c>
+      <c r="E19" s="47" t="s">
+        <v>323</v>
+      </c>
+      <c r="F19" s="47" t="s">
         <v>119</v>
       </c>
-      <c r="G19" s="37" t="s">
-        <v>159</v>
-      </c>
-      <c r="H19" s="37" t="s">
+      <c r="G19" s="47" t="s">
+        <v>324</v>
+      </c>
+      <c r="H19" s="47" t="s">
         <v>205</v>
       </c>
-      <c r="I19" s="37" t="s">
-        <v>246</v>
+      <c r="I19" s="47" t="s">
+        <v>242</v>
       </c>
       <c r="J19" s="47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K19" s="37">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="L19" s="55"/>
+        <v>5</v>
+      </c>
+      <c r="L19" s="54"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="44"/>
-      <c r="C20" s="48"/>
-      <c r="D20" s="74" t="s">
-        <v>285</v>
+      <c r="B20" s="44">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C20" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="62" t="s">
+        <v>281</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>286</v>
+        <v>56</v>
       </c>
       <c r="F20" s="37" t="s">
         <v>119</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>287</v>
+        <v>152</v>
       </c>
       <c r="H20" s="37" t="s">
         <v>205</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>333</v>
+        <v>237</v>
       </c>
       <c r="J20" s="37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K20" s="37">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L20" s="55"/>
+        <v>15</v>
+      </c>
+      <c r="L20" s="54"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="45">
-        <f t="shared" ref="B21:B78" si="2">ROW(B21) - ROW($B$9)</f>
+      <c r="B21" s="44">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="C21" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="75" t="s">
-        <v>288</v>
-      </c>
-      <c r="E21" s="47" t="s">
-        <v>57</v>
-      </c>
-      <c r="F21" s="47" t="s">
+      <c r="D21" s="63" t="s">
+        <v>282</v>
+      </c>
+      <c r="E21" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" s="37" t="s">
         <v>119</v>
       </c>
-      <c r="G21" s="47" t="s">
-        <v>153</v>
-      </c>
-      <c r="H21" s="47" t="s">
+      <c r="G21" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="H21" s="37" t="s">
         <v>205</v>
       </c>
-      <c r="I21" s="47" t="s">
-        <v>238</v>
+      <c r="I21" s="37" t="s">
+        <v>246</v>
       </c>
       <c r="J21" s="47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K21" s="37">
         <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="L21" s="54"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="62" t="s">
+        <v>283</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>284</v>
+      </c>
+      <c r="F22" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="G22" s="37" t="s">
+        <v>285</v>
+      </c>
+      <c r="H22" s="37" t="s">
+        <v>205</v>
+      </c>
+      <c r="I22" s="37" t="s">
+        <v>315</v>
+      </c>
+      <c r="J22" s="37">
+        <v>1</v>
+      </c>
+      <c r="K22" s="37">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L21" s="55"/>
-    </row>
-    <row r="22" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="45">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
-      <c r="C22" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="F22" s="47" t="s">
-        <v>125</v>
-      </c>
-      <c r="G22" s="47" t="s">
-        <v>160</v>
-      </c>
-      <c r="H22" s="47" t="s">
-        <v>209</v>
-      </c>
-      <c r="I22" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="J22" s="47">
-        <v>2</v>
-      </c>
-      <c r="K22" s="37">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L22" s="55"/>
+      <c r="L22" s="54"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="44">
-        <f>ROW(B23) - ROW($B$9)</f>
+      <c r="B23" s="45">
+        <f t="shared" ref="B23:B80" si="2">ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
       <c r="C23" s="48" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="74" t="s">
-        <v>28</v>
-      </c>
-      <c r="E23" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="F23" s="37" t="s">
-        <v>126</v>
-      </c>
-      <c r="G23" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="H23" s="37" t="s">
-        <v>210</v>
+        <v>7</v>
+      </c>
+      <c r="D23" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="E23" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="F23" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="G23" s="47" t="s">
+        <v>153</v>
+      </c>
+      <c r="H23" s="47" t="s">
+        <v>205</v>
       </c>
       <c r="I23" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="J23" s="37">
+        <v>238</v>
+      </c>
+      <c r="J23" s="47">
         <v>1</v>
       </c>
       <c r="K23" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L23" s="55"/>
-    </row>
-    <row r="24" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+      <c r="L23" s="54"/>
+    </row>
+    <row r="24" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="45">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="C24" s="49" t="s">
+      <c r="C24" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="75" t="s">
-        <v>289</v>
+      <c r="D24" s="63" t="s">
+        <v>27</v>
       </c>
       <c r="E24" s="47" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F24" s="47" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G24" s="47" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H24" s="47" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I24" s="47" t="s">
         <v>270</v>
       </c>
       <c r="J24" s="47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K24" s="37">
         <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="L24" s="55"/>
+        <v>10</v>
+      </c>
+      <c r="L24" s="54"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
@@ -2806,34 +2797,34 @@
         <v>16</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="74" t="s">
-        <v>29</v>
+        <v>8</v>
+      </c>
+      <c r="D25" s="62" t="s">
+        <v>28</v>
       </c>
       <c r="E25" s="37" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F25" s="37" t="s">
         <v>126</v>
       </c>
       <c r="G25" s="37" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H25" s="37" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I25" s="47" t="s">
         <v>270</v>
       </c>
       <c r="J25" s="37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K25" s="37">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L25" s="55"/>
+        <v>5</v>
+      </c>
+      <c r="L25" s="54"/>
     </row>
     <row r="26" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
@@ -2842,34 +2833,34 @@
         <v>17</v>
       </c>
       <c r="C26" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="63" t="s">
+        <v>325</v>
+      </c>
+      <c r="E26" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" s="47" t="s">
+        <v>127</v>
+      </c>
+      <c r="G26" s="47" t="s">
+        <v>162</v>
+      </c>
+      <c r="H26" s="47" t="s">
+        <v>211</v>
+      </c>
+      <c r="I26" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="J26" s="47">
+        <v>2</v>
+      </c>
+      <c r="K26" s="37">
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="D26" s="75" t="s">
-        <v>30</v>
-      </c>
-      <c r="E26" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="F26" s="47" t="s">
-        <v>128</v>
-      </c>
-      <c r="G26" s="47" t="s">
-        <v>164</v>
-      </c>
-      <c r="H26" s="47" t="s">
-        <v>213</v>
-      </c>
-      <c r="I26" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="J26" s="47">
-        <v>1</v>
-      </c>
-      <c r="K26" s="37">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L26" s="55"/>
+      <c r="L26" s="54"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
@@ -2878,142 +2869,142 @@
         <v>18</v>
       </c>
       <c r="C27" s="48" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="74" t="s">
-        <v>290</v>
+        <v>9</v>
+      </c>
+      <c r="D27" s="62" t="s">
+        <v>29</v>
       </c>
       <c r="E27" s="37" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F27" s="37" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G27" s="37" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H27" s="37" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="I27" s="47" t="s">
         <v>270</v>
       </c>
       <c r="J27" s="37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K27" s="37">
         <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="L27" s="55"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="L27" s="54"/>
+    </row>
+    <row r="28" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="45">
         <f t="shared" si="2"/>
         <v>19</v>
       </c>
       <c r="C28" s="49" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" s="75" t="s">
-        <v>291</v>
+        <v>10</v>
+      </c>
+      <c r="D28" s="63" t="s">
+        <v>30</v>
       </c>
       <c r="E28" s="47" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F28" s="47" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G28" s="47" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H28" s="47" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I28" s="47" t="s">
         <v>270</v>
       </c>
       <c r="J28" s="47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K28" s="37">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="L28" s="55"/>
-    </row>
-    <row r="29" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="L28" s="54"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="44">
         <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
       <c r="C29" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="D29" s="74" t="s">
-        <v>31</v>
+        <v>11</v>
+      </c>
+      <c r="D29" s="62" t="s">
+        <v>326</v>
       </c>
       <c r="E29" s="37" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F29" s="37" t="s">
-        <v>269</v>
+        <v>129</v>
       </c>
       <c r="G29" s="37" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H29" s="37" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="I29" s="47" t="s">
         <v>270</v>
       </c>
       <c r="J29" s="37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K29" s="37">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L29" s="55"/>
-    </row>
-    <row r="30" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="L29" s="54"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="45">
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="C30" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" s="75" t="s">
-        <v>32</v>
+        <v>11</v>
+      </c>
+      <c r="D30" s="63" t="s">
+        <v>327</v>
       </c>
       <c r="E30" s="47" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F30" s="47" t="s">
-        <v>269</v>
+        <v>130</v>
       </c>
       <c r="G30" s="47" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H30" s="47" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I30" s="47" t="s">
         <v>270</v>
       </c>
       <c r="J30" s="47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K30" s="37">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L30" s="55"/>
+        <v>20</v>
+      </c>
+      <c r="L30" s="54"/>
     </row>
     <row r="31" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
@@ -3022,22 +3013,22 @@
         <v>22</v>
       </c>
       <c r="C31" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="D31" s="74" t="s">
-        <v>33</v>
+        <v>12</v>
+      </c>
+      <c r="D31" s="62" t="s">
+        <v>31</v>
       </c>
       <c r="E31" s="37" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F31" s="37" t="s">
         <v>269</v>
       </c>
       <c r="G31" s="37" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H31" s="37" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I31" s="47" t="s">
         <v>270</v>
@@ -3049,9 +3040,9 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L31" s="55"/>
-    </row>
-    <row r="32" spans="1:12" ht="48" x14ac:dyDescent="0.25">
+      <c r="L31" s="54"/>
+    </row>
+    <row r="32" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="45">
         <f t="shared" si="2"/>
@@ -3060,167 +3051,167 @@
       <c r="C32" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="D32" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="E32" s="57" t="s">
-        <v>77</v>
-      </c>
-      <c r="F32" s="57" t="s">
+      <c r="D32" s="63" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="F32" s="47" t="s">
         <v>269</v>
       </c>
-      <c r="G32" s="57" t="s">
-        <v>131</v>
-      </c>
-      <c r="H32" s="57" t="s">
-        <v>218</v>
-      </c>
-      <c r="I32" s="57" t="s">
-        <v>247</v>
-      </c>
-      <c r="J32" s="57">
+      <c r="G32" s="47" t="s">
+        <v>168</v>
+      </c>
+      <c r="H32" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="I32" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="J32" s="47">
         <v>1</v>
       </c>
       <c r="K32" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L32" s="55"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L32" s="54"/>
+    </row>
+    <row r="33" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="44">
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
       <c r="C33" s="48" t="s">
-        <v>15</v>
-      </c>
-      <c r="D33" s="74" t="s">
-        <v>35</v>
+        <v>14</v>
+      </c>
+      <c r="D33" s="62" t="s">
+        <v>33</v>
       </c>
       <c r="E33" s="37" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>132</v>
+        <v>269</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>337</v>
+        <v>169</v>
       </c>
       <c r="H33" s="37" t="s">
-        <v>219</v>
-      </c>
-      <c r="I33" s="37" t="s">
+        <v>217</v>
+      </c>
+      <c r="I33" s="47" t="s">
         <v>270</v>
       </c>
       <c r="J33" s="37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K33" s="37">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L33" s="55"/>
-    </row>
-    <row r="34" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="L33" s="54"/>
+    </row>
+    <row r="34" spans="1:12" ht="48" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="45">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
       <c r="C34" s="49" t="s">
-        <v>16</v>
-      </c>
-      <c r="D34" s="75" t="s">
-        <v>36</v>
-      </c>
-      <c r="E34" s="47" t="s">
-        <v>79</v>
-      </c>
-      <c r="F34" s="47" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="56" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" s="56" t="s">
+        <v>77</v>
+      </c>
+      <c r="F34" s="56" t="s">
         <v>269</v>
       </c>
-      <c r="G34" s="47" t="s">
-        <v>170</v>
-      </c>
-      <c r="H34" s="47" t="s">
-        <v>220</v>
-      </c>
-      <c r="I34" s="47" t="s">
-        <v>248</v>
-      </c>
-      <c r="J34" s="47">
+      <c r="G34" s="56" t="s">
+        <v>131</v>
+      </c>
+      <c r="H34" s="56" t="s">
+        <v>218</v>
+      </c>
+      <c r="I34" s="56" t="s">
+        <v>247</v>
+      </c>
+      <c r="J34" s="56">
         <v>1</v>
       </c>
       <c r="K34" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L34" s="55"/>
-    </row>
-    <row r="35" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+      <c r="L34" s="54"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="44">
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
       <c r="C35" s="48" t="s">
-        <v>16</v>
-      </c>
-      <c r="D35" s="74" t="s">
-        <v>37</v>
+        <v>15</v>
+      </c>
+      <c r="D35" s="62" t="s">
+        <v>35</v>
       </c>
       <c r="E35" s="37" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F35" s="37" t="s">
-        <v>269</v>
-      </c>
-      <c r="G35" s="37" t="s">
-        <v>171</v>
+        <v>132</v>
+      </c>
+      <c r="G35" s="55">
+        <v>61300211121</v>
       </c>
       <c r="H35" s="37" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I35" s="37" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="J35" s="37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K35" s="37">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L35" s="55"/>
-    </row>
-    <row r="36" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="L35" s="54"/>
+    </row>
+    <row r="36" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="45">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
       <c r="C36" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="D36" s="75" t="s">
-        <v>38</v>
+        <v>16</v>
+      </c>
+      <c r="D36" s="63" t="s">
+        <v>36</v>
       </c>
       <c r="E36" s="47" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F36" s="47" t="s">
-        <v>133</v>
+        <v>269</v>
       </c>
       <c r="G36" s="47" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H36" s="47" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I36" s="47" t="s">
-        <v>270</v>
+        <v>248</v>
       </c>
       <c r="J36" s="47">
         <v>1</v>
@@ -3229,34 +3220,34 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L36" s="55"/>
-    </row>
-    <row r="37" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="L36" s="54"/>
+    </row>
+    <row r="37" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="44">
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
       <c r="C37" s="48" t="s">
-        <v>17</v>
-      </c>
-      <c r="D37" s="74" t="s">
-        <v>39</v>
+        <v>16</v>
+      </c>
+      <c r="D37" s="62" t="s">
+        <v>37</v>
       </c>
       <c r="E37" s="37" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F37" s="37" t="s">
-        <v>133</v>
+        <v>269</v>
       </c>
       <c r="G37" s="37" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H37" s="37" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I37" s="37" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="J37" s="37">
         <v>1</v>
@@ -3265,7 +3256,7 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L37" s="55"/>
+      <c r="L37" s="54"/>
     </row>
     <row r="38" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
@@ -3276,22 +3267,22 @@
       <c r="C38" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="75" t="s">
-        <v>40</v>
+      <c r="D38" s="63" t="s">
+        <v>38</v>
       </c>
       <c r="E38" s="47" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F38" s="47" t="s">
         <v>133</v>
       </c>
       <c r="G38" s="47" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H38" s="47" t="s">
         <v>221</v>
       </c>
-      <c r="I38" s="37" t="s">
+      <c r="I38" s="47" t="s">
         <v>270</v>
       </c>
       <c r="J38" s="47">
@@ -3301,31 +3292,31 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L38" s="55"/>
-    </row>
-    <row r="39" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+      <c r="L38" s="54"/>
+    </row>
+    <row r="39" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="44">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
       <c r="C39" s="48" t="s">
-        <v>18</v>
-      </c>
-      <c r="D39" s="74" t="s">
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="D39" s="62" t="s">
+        <v>39</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H39" s="37" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I39" s="37" t="s">
         <v>270</v>
@@ -3337,7 +3328,7 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L39" s="55"/>
+      <c r="L39" s="54"/>
     </row>
     <row r="40" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
@@ -3346,58 +3337,58 @@
         <v>31</v>
       </c>
       <c r="C40" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" s="57" t="s">
-        <v>292</v>
-      </c>
-      <c r="E40" s="57" t="s">
-        <v>85</v>
-      </c>
-      <c r="F40" s="57" t="s">
-        <v>269</v>
-      </c>
-      <c r="G40" s="57" t="s">
-        <v>270</v>
-      </c>
-      <c r="H40" s="57" t="s">
-        <v>270</v>
-      </c>
-      <c r="I40" s="56" t="s">
-        <v>270</v>
-      </c>
-      <c r="J40" s="57">
-        <v>14</v>
+        <v>17</v>
+      </c>
+      <c r="D40" s="63" t="s">
+        <v>40</v>
+      </c>
+      <c r="E40" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="F40" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="G40" s="47" t="s">
+        <v>174</v>
+      </c>
+      <c r="H40" s="47" t="s">
+        <v>221</v>
+      </c>
+      <c r="I40" s="37" t="s">
+        <v>270</v>
+      </c>
+      <c r="J40" s="47">
+        <v>1</v>
       </c>
       <c r="K40" s="37">
         <f t="shared" si="1"/>
-        <v>70</v>
-      </c>
-      <c r="L40" s="55"/>
-    </row>
-    <row r="41" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="L40" s="54"/>
+    </row>
+    <row r="41" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="44">
         <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
       <c r="C41" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" s="74" t="s">
-        <v>42</v>
+        <v>18</v>
+      </c>
+      <c r="D41" s="62" t="s">
+        <v>41</v>
       </c>
       <c r="E41" s="37" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F41" s="37" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G41" s="37" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H41" s="37" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I41" s="37" t="s">
         <v>270</v>
@@ -3409,151 +3400,151 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L41" s="55"/>
-    </row>
-    <row r="42" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+      <c r="L41" s="54"/>
+    </row>
+    <row r="42" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="45">
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
       <c r="C42" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="D42" s="75" t="s">
-        <v>293</v>
-      </c>
-      <c r="E42" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="F42" s="47" t="s">
-        <v>136</v>
-      </c>
-      <c r="G42" s="47" t="s">
-        <v>177</v>
-      </c>
-      <c r="H42" s="47" t="s">
-        <v>224</v>
-      </c>
-      <c r="I42" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="J42" s="47">
-        <v>2</v>
+        <v>19</v>
+      </c>
+      <c r="D42" s="56" t="s">
+        <v>328</v>
+      </c>
+      <c r="E42" s="56" t="s">
+        <v>85</v>
+      </c>
+      <c r="F42" s="56" t="s">
+        <v>269</v>
+      </c>
+      <c r="G42" s="56" t="s">
+        <v>270</v>
+      </c>
+      <c r="H42" s="56" t="s">
+        <v>270</v>
+      </c>
+      <c r="I42" s="55" t="s">
+        <v>270</v>
+      </c>
+      <c r="J42" s="56">
+        <v>15</v>
       </c>
       <c r="K42" s="37">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L42" s="55"/>
-    </row>
-    <row r="43" spans="1:12" ht="48" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="L42" s="54"/>
+    </row>
+    <row r="43" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="44">
-        <f t="shared" si="2"/>
+        <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
       </c>
       <c r="C43" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="D43" s="74" t="s">
-        <v>43</v>
+      <c r="D43" s="62" t="s">
+        <v>42</v>
       </c>
       <c r="E43" s="37" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F43" s="37" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G43" s="37" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H43" s="37" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I43" s="37" t="s">
         <v>270</v>
       </c>
       <c r="J43" s="37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K43" s="37">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="L43" s="55"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="L43" s="54"/>
+    </row>
+    <row r="44" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="45">
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
       <c r="C44" s="49" t="s">
-        <v>21</v>
-      </c>
-      <c r="D44" s="75" t="s">
-        <v>294</v>
+        <v>20</v>
+      </c>
+      <c r="D44" s="63" t="s">
+        <v>329</v>
       </c>
       <c r="E44" s="47" t="s">
-        <v>295</v>
+        <v>87</v>
       </c>
       <c r="F44" s="47" t="s">
-        <v>296</v>
+        <v>136</v>
       </c>
       <c r="G44" s="47" t="s">
-        <v>297</v>
+        <v>177</v>
       </c>
       <c r="H44" s="47" t="s">
-        <v>205</v>
-      </c>
-      <c r="I44" s="47" t="s">
-        <v>334</v>
+        <v>224</v>
+      </c>
+      <c r="I44" s="37" t="s">
+        <v>270</v>
       </c>
       <c r="J44" s="47">
-        <v>1</v>
-      </c>
-      <c r="K44" s="47">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L44" s="55"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="K44" s="37">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="L44" s="54"/>
+    </row>
+    <row r="45" spans="1:12" ht="48" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
-      <c r="B45" s="45">
-        <f>ROW(B45) - ROW($B$9)</f>
+      <c r="B45" s="44">
+        <f t="shared" si="2"/>
         <v>36</v>
       </c>
-      <c r="C45" s="49" t="s">
-        <v>21</v>
-      </c>
-      <c r="D45" s="75" t="s">
-        <v>298</v>
-      </c>
-      <c r="E45" s="47" t="s">
-        <v>89</v>
-      </c>
-      <c r="F45" s="47" t="s">
-        <v>138</v>
-      </c>
-      <c r="G45" s="47" t="s">
-        <v>179</v>
-      </c>
-      <c r="H45" s="47" t="s">
-        <v>205</v>
-      </c>
-      <c r="I45" s="47" t="s">
-        <v>250</v>
-      </c>
-      <c r="J45" s="47">
+      <c r="C45" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45" s="62" t="s">
+        <v>43</v>
+      </c>
+      <c r="E45" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="F45" s="37" t="s">
+        <v>137</v>
+      </c>
+      <c r="G45" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="H45" s="37" t="s">
+        <v>225</v>
+      </c>
+      <c r="I45" s="37" t="s">
+        <v>270</v>
+      </c>
+      <c r="J45" s="37">
         <v>4</v>
       </c>
       <c r="K45" s="37">
-        <f>J45*5</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L45" s="55"/>
+      <c r="L45" s="54"/>
     </row>
     <row r="46" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
@@ -3564,8 +3555,8 @@
       <c r="C46" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D46" s="75" t="s">
-        <v>299</v>
+      <c r="D46" s="63" t="s">
+        <v>330</v>
       </c>
       <c r="E46" s="37" t="s">
         <v>90</v>
@@ -3583,85 +3574,85 @@
         <v>251</v>
       </c>
       <c r="J46" s="37">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K46" s="37">
         <f t="shared" si="1"/>
-        <v>65</v>
-      </c>
-      <c r="L46" s="55"/>
-    </row>
-    <row r="47" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="L46" s="54"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
-      <c r="B47" s="44">
+      <c r="B47" s="45">
         <f t="shared" si="2"/>
         <v>38</v>
       </c>
-      <c r="C47" s="48" t="s">
+      <c r="C47" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D47" s="74" t="s">
-        <v>300</v>
-      </c>
-      <c r="E47" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="F47" s="37" t="s">
-        <v>139</v>
-      </c>
-      <c r="G47" s="37" t="s">
-        <v>181</v>
-      </c>
-      <c r="H47" s="37" t="s">
-        <v>226</v>
-      </c>
-      <c r="I47" s="37" t="s">
-        <v>252</v>
-      </c>
-      <c r="J47" s="37">
+      <c r="D47" s="62" t="s">
+        <v>331</v>
+      </c>
+      <c r="E47" s="47" t="s">
+        <v>332</v>
+      </c>
+      <c r="F47" s="47" t="s">
+        <v>138</v>
+      </c>
+      <c r="G47" s="47" t="s">
+        <v>333</v>
+      </c>
+      <c r="H47" s="47" t="s">
+        <v>334</v>
+      </c>
+      <c r="I47" s="47" t="s">
+        <v>340</v>
+      </c>
+      <c r="J47" s="47">
         <v>1</v>
       </c>
       <c r="K47" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L47" s="55"/>
+      <c r="L47" s="54"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
-      <c r="B48" s="44">
+      <c r="B48" s="45">
         <f t="shared" si="2"/>
         <v>39</v>
       </c>
       <c r="C48" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D48" s="75" t="s">
-        <v>301</v>
-      </c>
-      <c r="E48" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="F48" s="37" t="s">
+      <c r="D48" s="63" t="s">
+        <v>287</v>
+      </c>
+      <c r="E48" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="F48" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="G48" s="37" t="s">
-        <v>184</v>
-      </c>
-      <c r="H48" s="37" t="s">
+      <c r="G48" s="47" t="s">
+        <v>179</v>
+      </c>
+      <c r="H48" s="47" t="s">
         <v>205</v>
       </c>
-      <c r="I48" s="37" t="s">
-        <v>255</v>
-      </c>
-      <c r="J48" s="37">
-        <v>1</v>
+      <c r="I48" s="47" t="s">
+        <v>250</v>
+      </c>
+      <c r="J48" s="47">
+        <v>4</v>
       </c>
       <c r="K48" s="37">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L48" s="55"/>
+        <v>20</v>
+      </c>
+      <c r="L48" s="54"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
@@ -3672,70 +3663,70 @@
       <c r="C49" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D49" s="74" t="s">
-        <v>302</v>
+      <c r="D49" s="62" t="s">
+        <v>335</v>
       </c>
       <c r="E49" s="47" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F49" s="47" t="s">
         <v>138</v>
       </c>
       <c r="G49" s="47" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H49" s="47" t="s">
         <v>205</v>
       </c>
       <c r="I49" s="47" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="J49" s="47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K49" s="37">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L49" s="55"/>
+        <v>15</v>
+      </c>
+      <c r="L49" s="54"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
-      <c r="B50" s="45">
+      <c r="B50" s="44">
         <f t="shared" si="2"/>
         <v>41</v>
       </c>
       <c r="C50" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D50" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="E50" s="47" t="s">
-        <v>97</v>
-      </c>
-      <c r="F50" s="47" t="s">
+      <c r="D50" s="63" t="s">
+        <v>336</v>
+      </c>
+      <c r="E50" s="37" t="s">
+        <v>337</v>
+      </c>
+      <c r="F50" s="37" t="s">
         <v>138</v>
       </c>
-      <c r="G50" s="47" t="s">
-        <v>187</v>
-      </c>
-      <c r="H50" s="47" t="s">
+      <c r="G50" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="H50" s="37" t="s">
         <v>205</v>
       </c>
-      <c r="I50" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="J50" s="47">
+      <c r="I50" s="37" t="s">
+        <v>341</v>
+      </c>
+      <c r="J50" s="37">
         <v>1</v>
       </c>
       <c r="K50" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L50" s="55"/>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L50" s="54"/>
+    </row>
+    <row r="51" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="44">
         <f t="shared" si="2"/>
@@ -3744,23 +3735,23 @@
       <c r="C51" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="D51" s="74" t="s">
-        <v>45</v>
+      <c r="D51" s="62" t="s">
+        <v>288</v>
       </c>
       <c r="E51" s="37" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="F51" s="37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G51" s="37" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="H51" s="37" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="I51" s="37" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="J51" s="37">
         <v>1</v>
@@ -3769,7 +3760,7 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L51" s="55"/>
+      <c r="L51" s="54"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
@@ -3780,32 +3771,32 @@
       <c r="C52" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D52" s="75" t="s">
-        <v>303</v>
+      <c r="D52" s="63" t="s">
+        <v>289</v>
       </c>
       <c r="E52" s="37" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F52" s="37" t="s">
         <v>138</v>
       </c>
       <c r="G52" s="37" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H52" s="37" t="s">
         <v>205</v>
       </c>
       <c r="I52" s="37" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="J52" s="37">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K52" s="37">
         <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="L52" s="55"/>
+        <v>5</v>
+      </c>
+      <c r="L52" s="54"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
@@ -3813,26 +3804,26 @@
         <f t="shared" si="2"/>
         <v>44</v>
       </c>
-      <c r="C53" s="48" t="s">
+      <c r="C53" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D53" s="74" t="s">
-        <v>304</v>
+      <c r="D53" s="62" t="s">
+        <v>290</v>
       </c>
       <c r="E53" s="47" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F53" s="47" t="s">
         <v>138</v>
       </c>
       <c r="G53" s="47" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="H53" s="47" t="s">
         <v>205</v>
       </c>
       <c r="I53" s="47" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J53" s="47">
         <v>1</v>
@@ -3841,79 +3832,79 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L53" s="55"/>
+      <c r="L53" s="54"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
-      <c r="B54" s="44">
+      <c r="B54" s="45">
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="C54" s="48" t="s">
+      <c r="C54" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D54" s="75" t="s">
-        <v>305</v>
-      </c>
-      <c r="E54" s="37" t="s">
-        <v>100</v>
-      </c>
-      <c r="F54" s="37" t="s">
+      <c r="D54" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="E54" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="F54" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="G54" s="37" t="s">
-        <v>190</v>
-      </c>
-      <c r="H54" s="37" t="s">
+      <c r="G54" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="H54" s="47" t="s">
         <v>205</v>
       </c>
-      <c r="I54" s="37" t="s">
-        <v>261</v>
-      </c>
-      <c r="J54" s="37">
-        <v>2</v>
+      <c r="I54" s="47" t="s">
+        <v>258</v>
+      </c>
+      <c r="J54" s="47">
+        <v>1</v>
       </c>
       <c r="K54" s="37">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L54" s="55"/>
+        <v>5</v>
+      </c>
+      <c r="L54" s="54"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
-      <c r="B55" s="45">
+      <c r="B55" s="44">
         <f t="shared" si="2"/>
         <v>46</v>
       </c>
-      <c r="C55" s="49" t="s">
+      <c r="C55" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="D55" s="74" t="s">
-        <v>306</v>
-      </c>
-      <c r="E55" s="47" t="s">
-        <v>101</v>
-      </c>
-      <c r="F55" s="47" t="s">
+      <c r="D55" s="62" t="s">
+        <v>45</v>
+      </c>
+      <c r="E55" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="F55" s="37" t="s">
         <v>138</v>
       </c>
-      <c r="G55" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="H55" s="47" t="s">
+      <c r="G55" s="37" t="s">
+        <v>188</v>
+      </c>
+      <c r="H55" s="37" t="s">
         <v>205</v>
       </c>
-      <c r="I55" s="47" t="s">
-        <v>262</v>
-      </c>
-      <c r="J55" s="47">
+      <c r="I55" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J55" s="37">
         <v>1</v>
       </c>
       <c r="K55" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L55" s="55"/>
+      <c r="L55" s="54"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
@@ -3921,35 +3912,35 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="C56" s="48" t="s">
+      <c r="C56" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D56" s="75" t="s">
-        <v>307</v>
+      <c r="D56" s="63" t="s">
+        <v>291</v>
       </c>
       <c r="E56" s="37" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F56" s="37" t="s">
         <v>138</v>
       </c>
       <c r="G56" s="37" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="H56" s="37" t="s">
         <v>205</v>
       </c>
       <c r="I56" s="37" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="J56" s="37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K56" s="37">
         <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="L56" s="55"/>
+        <v>30</v>
+      </c>
+      <c r="L56" s="54"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
@@ -3957,143 +3948,143 @@
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="C57" s="49" t="s">
+      <c r="C57" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="D57" s="74" t="s">
-        <v>308</v>
+      <c r="D57" s="62" t="s">
+        <v>292</v>
       </c>
       <c r="E57" s="47" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F57" s="47" t="s">
         <v>138</v>
       </c>
       <c r="G57" s="47" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="H57" s="47" t="s">
         <v>205</v>
       </c>
       <c r="I57" s="47" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="J57" s="47">
+        <v>1</v>
+      </c>
+      <c r="K57" s="37">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="K57" s="37">
-        <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="L57" s="55"/>
+      <c r="L57" s="54"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
-      <c r="B58" s="45">
+      <c r="B58" s="44">
         <f t="shared" si="2"/>
         <v>49</v>
       </c>
-      <c r="C58" s="49" t="s">
+      <c r="C58" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="D58" s="75" t="s">
-        <v>309</v>
-      </c>
-      <c r="E58" s="47" t="s">
-        <v>103</v>
-      </c>
-      <c r="F58" s="47" t="s">
+      <c r="D58" s="63" t="s">
+        <v>293</v>
+      </c>
+      <c r="E58" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="F58" s="37" t="s">
         <v>138</v>
       </c>
-      <c r="G58" s="47" t="s">
-        <v>193</v>
-      </c>
-      <c r="H58" s="47" t="s">
+      <c r="G58" s="37" t="s">
+        <v>190</v>
+      </c>
+      <c r="H58" s="37" t="s">
         <v>205</v>
       </c>
-      <c r="I58" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="J58" s="47">
+      <c r="I58" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="J58" s="37">
         <v>2</v>
       </c>
       <c r="K58" s="37">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L58" s="55"/>
+      <c r="L58" s="54"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
-      <c r="B59" s="44">
-        <f>ROW(B59) - ROW($B$9)</f>
+      <c r="B59" s="45">
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="C59" s="48" t="s">
+      <c r="C59" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D59" s="37" t="s">
-        <v>310</v>
-      </c>
-      <c r="E59" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="F59" s="37" t="s">
+      <c r="D59" s="62" t="s">
+        <v>294</v>
+      </c>
+      <c r="E59" s="47" t="s">
+        <v>101</v>
+      </c>
+      <c r="F59" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="G59" s="37" t="s">
-        <v>182</v>
-      </c>
-      <c r="H59" s="37" t="s">
+      <c r="G59" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="H59" s="47" t="s">
         <v>205</v>
       </c>
-      <c r="I59" s="37" t="s">
-        <v>253</v>
-      </c>
-      <c r="J59" s="37">
-        <v>2</v>
+      <c r="I59" s="47" t="s">
+        <v>262</v>
+      </c>
+      <c r="J59" s="47">
+        <v>1</v>
       </c>
       <c r="K59" s="37">
-        <f>J59*5</f>
-        <v>10</v>
-      </c>
-      <c r="L59" s="55"/>
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="L59" s="54"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="44">
-        <f>ROW(B60) - ROW($B$9)</f>
+        <f t="shared" si="2"/>
         <v>51</v>
       </c>
       <c r="C60" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="D60" s="74" t="s">
-        <v>311</v>
+      <c r="D60" s="63" t="s">
+        <v>295</v>
       </c>
       <c r="E60" s="37" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F60" s="37" t="s">
         <v>138</v>
       </c>
       <c r="G60" s="37" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H60" s="37" t="s">
         <v>205</v>
       </c>
       <c r="I60" s="37" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="J60" s="37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K60" s="37">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="L60" s="55"/>
+        <v>25</v>
+      </c>
+      <c r="L60" s="54"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
@@ -4104,358 +4095,358 @@
       <c r="C61" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D61" s="75" t="s">
-        <v>312</v>
+      <c r="D61" s="62" t="s">
+        <v>296</v>
       </c>
       <c r="E61" s="47" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="F61" s="47" t="s">
         <v>138</v>
       </c>
       <c r="G61" s="47" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="H61" s="47" t="s">
         <v>205</v>
       </c>
       <c r="I61" s="47" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="J61" s="47">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K61" s="37">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L61" s="55"/>
-    </row>
-    <row r="62" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="L61" s="54"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="45">
         <f t="shared" si="2"/>
         <v>53</v>
       </c>
       <c r="C62" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="D62" s="57" t="s">
-        <v>313</v>
-      </c>
-      <c r="E62" s="57" t="s">
-        <v>106</v>
-      </c>
-      <c r="F62" s="57" t="s">
-        <v>269</v>
-      </c>
-      <c r="G62" s="57" t="s">
-        <v>140</v>
-      </c>
-      <c r="H62" s="57" t="s">
-        <v>270</v>
-      </c>
-      <c r="I62" s="58" t="s">
-        <v>270</v>
-      </c>
-      <c r="J62" s="57">
+        <v>21</v>
+      </c>
+      <c r="D62" s="63" t="s">
+        <v>297</v>
+      </c>
+      <c r="E62" s="47" t="s">
+        <v>103</v>
+      </c>
+      <c r="F62" s="47" t="s">
+        <v>138</v>
+      </c>
+      <c r="G62" s="47" t="s">
+        <v>193</v>
+      </c>
+      <c r="H62" s="47" t="s">
+        <v>205</v>
+      </c>
+      <c r="I62" s="47" t="s">
+        <v>264</v>
+      </c>
+      <c r="J62" s="47">
+        <v>2</v>
+      </c>
+      <c r="K62" s="37">
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="K62" s="37">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="L62" s="55"/>
-    </row>
-    <row r="63" spans="1:12" ht="48" x14ac:dyDescent="0.25">
+      <c r="L62" s="54"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="44">
         <f>ROW(B63) - ROW($B$9)</f>
         <v>54</v>
       </c>
       <c r="C63" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="D63" s="74" t="s">
-        <v>314</v>
+        <v>21</v>
+      </c>
+      <c r="D63" s="62" t="s">
+        <v>298</v>
       </c>
       <c r="E63" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="F63" s="47" t="s">
-        <v>269</v>
+        <v>104</v>
+      </c>
+      <c r="F63" s="37" t="s">
+        <v>138</v>
       </c>
       <c r="G63" s="37" t="s">
-        <v>142</v>
+        <v>194</v>
       </c>
       <c r="H63" s="37" t="s">
-        <v>227</v>
-      </c>
-      <c r="I63" s="47" t="s">
-        <v>270</v>
+        <v>205</v>
+      </c>
+      <c r="I63" s="37" t="s">
+        <v>265</v>
       </c>
       <c r="J63" s="37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K63" s="37">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L63" s="55"/>
-    </row>
-    <row r="64" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="L63" s="54"/>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="45">
-        <f>ROW(B64) - ROW($B$9)</f>
+        <f t="shared" si="2"/>
         <v>55</v>
       </c>
-      <c r="C64" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="D64" s="75" t="s">
-        <v>315</v>
+      <c r="C64" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="D64" s="63" t="s">
+        <v>299</v>
       </c>
       <c r="E64" s="47" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F64" s="47" t="s">
+        <v>138</v>
+      </c>
+      <c r="G64" s="47" t="s">
+        <v>195</v>
+      </c>
+      <c r="H64" s="47" t="s">
+        <v>205</v>
+      </c>
+      <c r="I64" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="J64" s="47">
+        <v>1</v>
+      </c>
+      <c r="K64" s="37">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="L64" s="54"/>
+    </row>
+    <row r="65" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="A65" s="1"/>
+      <c r="B65" s="45">
+        <f t="shared" si="2"/>
+        <v>56</v>
+      </c>
+      <c r="C65" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="D65" s="56" t="s">
+        <v>300</v>
+      </c>
+      <c r="E65" s="56" t="s">
+        <v>106</v>
+      </c>
+      <c r="F65" s="56" t="s">
         <v>269</v>
       </c>
-      <c r="G64" s="47" t="s">
-        <v>196</v>
-      </c>
-      <c r="H64" s="47" t="s">
-        <v>228</v>
-      </c>
-      <c r="I64" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="J64" s="47">
-        <v>1</v>
-      </c>
-      <c r="K64" s="37">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L64" s="55"/>
-    </row>
-    <row r="65" spans="1:12" ht="48" x14ac:dyDescent="0.25">
-      <c r="A65" s="1"/>
-      <c r="B65" s="44">
-        <f>ROW(B65) - ROW($B$9)</f>
-        <v>56</v>
-      </c>
-      <c r="C65" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="D65" s="74" t="s">
-        <v>316</v>
-      </c>
-      <c r="E65" s="37" t="s">
-        <v>110</v>
-      </c>
-      <c r="F65" s="47" t="s">
-        <v>269</v>
-      </c>
-      <c r="G65" s="37" t="s">
-        <v>197</v>
-      </c>
-      <c r="H65" s="37" t="s">
-        <v>227</v>
-      </c>
-      <c r="I65" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="J65" s="37">
-        <v>4</v>
+      <c r="G65" s="56" t="s">
+        <v>140</v>
+      </c>
+      <c r="H65" s="56" t="s">
+        <v>270</v>
+      </c>
+      <c r="I65" s="57" t="s">
+        <v>270</v>
+      </c>
+      <c r="J65" s="56">
+        <v>10</v>
       </c>
       <c r="K65" s="37">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="L65" s="55"/>
+        <v>50</v>
+      </c>
+      <c r="L65" s="54"/>
     </row>
     <row r="66" spans="1:12" ht="48" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
-      <c r="B66" s="45">
-        <f t="shared" si="2"/>
+      <c r="B66" s="44">
+        <f>ROW(B66) - ROW($B$9)</f>
         <v>57</v>
       </c>
-      <c r="C66" s="49" t="s">
+      <c r="C66" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="D66" s="75" t="s">
-        <v>317</v>
-      </c>
-      <c r="E66" s="47" t="s">
-        <v>107</v>
+      <c r="D66" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="E66" s="37" t="s">
+        <v>108</v>
       </c>
       <c r="F66" s="47" t="s">
         <v>269</v>
       </c>
-      <c r="G66" s="47" t="s">
-        <v>141</v>
-      </c>
-      <c r="H66" s="47" t="s">
+      <c r="G66" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="H66" s="37" t="s">
         <v>227</v>
       </c>
       <c r="I66" s="47" t="s">
         <v>270</v>
       </c>
-      <c r="J66" s="47">
-        <v>1</v>
+      <c r="J66" s="37">
+        <v>2</v>
       </c>
       <c r="K66" s="37">
         <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L66" s="54"/>
+    </row>
+    <row r="67" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A67" s="1"/>
+      <c r="B67" s="45">
+        <f>ROW(B67) - ROW($B$9)</f>
+        <v>58</v>
+      </c>
+      <c r="C67" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="D67" s="47" t="s">
+        <v>302</v>
+      </c>
+      <c r="E67" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="F67" s="47" t="s">
+        <v>269</v>
+      </c>
+      <c r="G67" s="47" t="s">
+        <v>196</v>
+      </c>
+      <c r="H67" s="47" t="s">
+        <v>228</v>
+      </c>
+      <c r="I67" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="J67" s="47">
+        <v>1</v>
+      </c>
+      <c r="K67" s="37">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L66" s="55"/>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" s="1"/>
-      <c r="B67" s="44">
-        <f t="shared" si="2"/>
-        <v>58</v>
-      </c>
-      <c r="C67" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="D67" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="E67" s="37" t="s">
-        <v>111</v>
-      </c>
-      <c r="F67" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="G67" s="37" t="s">
-        <v>198</v>
-      </c>
-      <c r="H67" s="37" t="s">
-        <v>230</v>
-      </c>
-      <c r="I67" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="J67" s="37">
-        <v>1</v>
-      </c>
-      <c r="K67" s="37">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L67" s="55"/>
-    </row>
-    <row r="68" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+      <c r="L67" s="54"/>
+    </row>
+    <row r="68" spans="1:12" ht="48" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="44">
-        <f t="shared" si="2"/>
+        <f>ROW(B68) - ROW($B$9)</f>
         <v>59</v>
       </c>
       <c r="C68" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="D68" s="47" t="s">
-        <v>47</v>
+        <v>23</v>
+      </c>
+      <c r="D68" s="37" t="s">
+        <v>303</v>
       </c>
       <c r="E68" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="F68" s="37" t="s">
-        <v>145</v>
+        <v>110</v>
+      </c>
+      <c r="F68" s="47" t="s">
+        <v>269</v>
       </c>
       <c r="G68" s="37" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H68" s="37" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="I68" s="47" t="s">
         <v>270</v>
       </c>
       <c r="J68" s="37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K68" s="37">
         <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="L68" s="54"/>
+    </row>
+    <row r="69" spans="1:12" ht="48" x14ac:dyDescent="0.25">
+      <c r="A69" s="1"/>
+      <c r="B69" s="45">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+      <c r="C69" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="D69" s="47" t="s">
+        <v>304</v>
+      </c>
+      <c r="E69" s="47" t="s">
+        <v>107</v>
+      </c>
+      <c r="F69" s="47" t="s">
+        <v>269</v>
+      </c>
+      <c r="G69" s="47" t="s">
+        <v>141</v>
+      </c>
+      <c r="H69" s="47" t="s">
+        <v>227</v>
+      </c>
+      <c r="I69" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="J69" s="47">
+        <v>1</v>
+      </c>
+      <c r="K69" s="37">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L68" s="55"/>
-    </row>
-    <row r="69" spans="1:12" ht="36" x14ac:dyDescent="0.25">
-      <c r="A69" s="1"/>
-      <c r="B69" s="44">
-        <f t="shared" si="2"/>
-        <v>60</v>
-      </c>
-      <c r="C69" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="D69" s="74" t="s">
-        <v>48</v>
-      </c>
-      <c r="E69" s="37" t="s">
-        <v>114</v>
-      </c>
-      <c r="F69" s="37" t="s">
-        <v>147</v>
-      </c>
-      <c r="G69" s="37" t="s">
-        <v>236</v>
-      </c>
-      <c r="H69" s="37" t="s">
-        <v>233</v>
-      </c>
-      <c r="I69" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="J69" s="37">
-        <v>1</v>
-      </c>
-      <c r="K69" s="37">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L69" s="55"/>
+      <c r="L69" s="54"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
-      <c r="B70" s="45">
+      <c r="B70" s="44">
         <f t="shared" si="2"/>
         <v>61</v>
       </c>
-      <c r="C70" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="D70" s="75" t="s">
-        <v>49</v>
-      </c>
-      <c r="E70" s="47" t="s">
-        <v>115</v>
-      </c>
-      <c r="F70" s="47" t="s">
-        <v>148</v>
-      </c>
-      <c r="G70" s="47" t="s">
-        <v>201</v>
-      </c>
-      <c r="H70" s="47" t="s">
-        <v>234</v>
+      <c r="C70" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="D70" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="E70" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="F70" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="G70" s="37" t="s">
+        <v>198</v>
+      </c>
+      <c r="H70" s="37" t="s">
+        <v>230</v>
       </c>
       <c r="I70" s="47" t="s">
         <v>270</v>
       </c>
-      <c r="J70" s="47">
+      <c r="J70" s="37">
         <v>1</v>
       </c>
       <c r="K70" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L70" s="55"/>
-    </row>
-    <row r="71" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="L70" s="54"/>
+    </row>
+    <row r="71" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="44">
         <f t="shared" si="2"/>
@@ -4464,20 +4455,20 @@
       <c r="C71" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="D71" s="75" t="s">
-        <v>50</v>
+      <c r="D71" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="E71" s="37" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F71" s="37" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="G71" s="37" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H71" s="37" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="I71" s="47" t="s">
         <v>270</v>
@@ -4489,43 +4480,43 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L71" s="55"/>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L71" s="54"/>
+    </row>
+    <row r="72" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
-      <c r="B72" s="45">
+      <c r="B72" s="44">
         <f t="shared" si="2"/>
         <v>63</v>
       </c>
-      <c r="C72" s="49" t="s">
+      <c r="C72" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="D72" s="75" t="s">
-        <v>51</v>
-      </c>
-      <c r="E72" s="47" t="s">
-        <v>117</v>
-      </c>
-      <c r="F72" s="47" t="s">
-        <v>150</v>
-      </c>
-      <c r="G72" s="47" t="s">
-        <v>203</v>
-      </c>
-      <c r="H72" s="47" t="s">
-        <v>212</v>
+      <c r="D72" s="62" t="s">
+        <v>48</v>
+      </c>
+      <c r="E72" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="F72" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="G72" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="H72" s="37" t="s">
+        <v>233</v>
       </c>
       <c r="I72" s="47" t="s">
         <v>270</v>
       </c>
-      <c r="J72" s="47">
+      <c r="J72" s="37">
         <v>1</v>
       </c>
       <c r="K72" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L72" s="55"/>
+      <c r="L72" s="54"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
@@ -4533,71 +4524,71 @@
         <f t="shared" si="2"/>
         <v>64</v>
       </c>
-      <c r="C73" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="D73" s="56" t="s">
-        <v>52</v>
-      </c>
-      <c r="E73" s="56" t="s">
-        <v>318</v>
-      </c>
-      <c r="F73" s="56" t="s">
-        <v>143</v>
-      </c>
-      <c r="G73" s="56" t="s">
-        <v>319</v>
-      </c>
-      <c r="H73" s="56" t="s">
-        <v>229</v>
-      </c>
-      <c r="I73" s="56" t="s">
-        <v>270</v>
-      </c>
-      <c r="J73" s="56">
-        <v>1</v>
-      </c>
-      <c r="K73" s="56">
+      <c r="C73" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="D73" s="63" t="s">
+        <v>49</v>
+      </c>
+      <c r="E73" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="F73" s="47" t="s">
+        <v>148</v>
+      </c>
+      <c r="G73" s="47" t="s">
+        <v>201</v>
+      </c>
+      <c r="H73" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="I73" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="J73" s="47">
+        <v>1</v>
+      </c>
+      <c r="K73" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L73" s="55"/>
+      <c r="L73" s="54"/>
     </row>
     <row r="74" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
-      <c r="B74" s="45">
+      <c r="B74" s="44">
         <f t="shared" si="2"/>
         <v>65</v>
       </c>
-      <c r="C74" s="49" t="s">
+      <c r="C74" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="D74" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="E74" s="47" t="s">
-        <v>320</v>
-      </c>
-      <c r="F74" s="47" t="s">
-        <v>146</v>
-      </c>
-      <c r="G74" s="47" t="s">
-        <v>321</v>
-      </c>
-      <c r="H74" s="47" t="s">
-        <v>322</v>
+      <c r="D74" s="63" t="s">
+        <v>50</v>
+      </c>
+      <c r="E74" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="F74" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="G74" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="H74" s="37" t="s">
+        <v>235</v>
       </c>
       <c r="I74" s="47" t="s">
         <v>270</v>
       </c>
-      <c r="J74" s="47">
+      <c r="J74" s="37">
         <v>1</v>
       </c>
       <c r="K74" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L74" s="55"/>
+      <c r="L74" s="54"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
@@ -4608,20 +4599,20 @@
       <c r="C75" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="D75" s="37" t="s">
-        <v>54</v>
+      <c r="D75" s="63" t="s">
+        <v>51</v>
       </c>
       <c r="E75" s="47" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F75" s="47" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="G75" s="47" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H75" s="47" t="s">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="I75" s="47" t="s">
         <v>270</v>
@@ -4630,70 +4621,70 @@
         <v>1</v>
       </c>
       <c r="K75" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="K75:K80" si="3">J75*5</f>
         <v>5</v>
       </c>
-      <c r="L75" s="55"/>
-    </row>
-    <row r="76" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="L75" s="54"/>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="45">
-        <f>ROW(B76) - ROW([1]Sheet1!$B$9)</f>
+        <f t="shared" si="2"/>
         <v>67</v>
       </c>
-      <c r="C76" s="49" t="s">
+      <c r="C76" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="D76" s="47" t="s">
-        <v>323</v>
-      </c>
-      <c r="E76" s="47" t="s">
-        <v>324</v>
-      </c>
-      <c r="F76" s="47" t="s">
-        <v>325</v>
-      </c>
-      <c r="G76" s="47" t="s">
-        <v>326</v>
-      </c>
-      <c r="H76" s="47" t="s">
-        <v>327</v>
-      </c>
-      <c r="I76" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="J76" s="47">
-        <v>1</v>
-      </c>
-      <c r="K76" s="47">
-        <f>J76*5</f>
+      <c r="D76" s="55" t="s">
+        <v>52</v>
+      </c>
+      <c r="E76" s="55" t="s">
+        <v>305</v>
+      </c>
+      <c r="F76" s="55" t="s">
+        <v>143</v>
+      </c>
+      <c r="G76" s="55" t="s">
+        <v>306</v>
+      </c>
+      <c r="H76" s="55" t="s">
+        <v>229</v>
+      </c>
+      <c r="I76" s="55" t="s">
+        <v>270</v>
+      </c>
+      <c r="J76" s="55">
+        <v>1</v>
+      </c>
+      <c r="K76" s="55">
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="L76" s="55"/>
-    </row>
-    <row r="77" spans="1:12" ht="48" x14ac:dyDescent="0.25">
+      <c r="L76" s="54"/>
+    </row>
+    <row r="77" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="45">
         <f t="shared" si="2"/>
         <v>68</v>
       </c>
       <c r="C77" s="49" t="s">
-        <v>328</v>
-      </c>
-      <c r="D77" s="37" t="s">
-        <v>329</v>
+        <v>24</v>
+      </c>
+      <c r="D77" s="47" t="s">
+        <v>53</v>
       </c>
       <c r="E77" s="47" t="s">
-        <v>330</v>
+        <v>307</v>
       </c>
       <c r="F77" s="47" t="s">
-        <v>270</v>
+        <v>146</v>
       </c>
       <c r="G77" s="47" t="s">
-        <v>270</v>
+        <v>308</v>
       </c>
       <c r="H77" s="47" t="s">
-        <v>270</v>
+        <v>309</v>
       </c>
       <c r="I77" s="47" t="s">
         <v>270</v>
@@ -4702,34 +4693,34 @@
         <v>1</v>
       </c>
       <c r="K77" s="37">
-        <f t="shared" ref="K77:K78" si="3">J77*5</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="L77" s="55"/>
-    </row>
-    <row r="78" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+      <c r="L77" s="54"/>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="45">
         <f t="shared" si="2"/>
         <v>69</v>
       </c>
       <c r="C78" s="49" t="s">
-        <v>331</v>
+        <v>24</v>
       </c>
       <c r="D78" s="37" t="s">
-        <v>329</v>
+        <v>54</v>
       </c>
       <c r="E78" s="47" t="s">
-        <v>332</v>
+        <v>113</v>
       </c>
       <c r="F78" s="47" t="s">
-        <v>270</v>
+        <v>146</v>
       </c>
       <c r="G78" s="47" t="s">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H78" s="47" t="s">
-        <v>270</v>
+        <v>231</v>
       </c>
       <c r="I78" s="47" t="s">
         <v>270</v>
@@ -4737,39 +4728,109 @@
       <c r="J78" s="47">
         <v>1</v>
       </c>
-      <c r="K78" s="37">
+      <c r="K78" s="69">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="L78" s="55"/>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L78" s="70"/>
+    </row>
+    <row r="79" spans="1:12" ht="48" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
-      <c r="B79" s="38"/>
-      <c r="C79" s="39"/>
-      <c r="D79" s="40"/>
-      <c r="E79" s="41"/>
-      <c r="F79" s="42"/>
-      <c r="G79" s="43"/>
-      <c r="H79" s="42"/>
-      <c r="I79" s="42"/>
-      <c r="J79" s="42"/>
-      <c r="K79" s="42"/>
-      <c r="L79" s="42"/>
-    </row>
-    <row r="80" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="45">
+        <f t="shared" si="2"/>
+        <v>70</v>
+      </c>
+      <c r="C79" s="49" t="s">
+        <v>310</v>
+      </c>
+      <c r="D79" s="37" t="s">
+        <v>311</v>
+      </c>
+      <c r="E79" s="47" t="s">
+        <v>312</v>
+      </c>
+      <c r="F79" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="G79" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="H79" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="I79" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="J79" s="47">
+        <v>1</v>
+      </c>
+      <c r="K79" s="69">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="L79" s="71"/>
+    </row>
+    <row r="80" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
-      <c r="B80" s="25"/>
-      <c r="C80" s="36"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="10"/>
-      <c r="F80" s="10"/>
-      <c r="G80" s="10"/>
-      <c r="H80" s="10"/>
-      <c r="I80" s="43"/>
-      <c r="J80" s="43"/>
-      <c r="K80" s="43"/>
-      <c r="L80" s="50"/>
+      <c r="B80" s="45">
+        <f t="shared" si="2"/>
+        <v>71</v>
+      </c>
+      <c r="C80" s="49" t="s">
+        <v>313</v>
+      </c>
+      <c r="D80" s="37" t="s">
+        <v>311</v>
+      </c>
+      <c r="E80" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="F80" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="G80" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="H80" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="I80" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="J80" s="47">
+        <v>1</v>
+      </c>
+      <c r="K80" s="69">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="L80" s="72"/>
+    </row>
+    <row r="81" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B81" s="38"/>
+      <c r="C81" s="39"/>
+      <c r="D81" s="40"/>
+      <c r="E81" s="41"/>
+      <c r="F81" s="42"/>
+      <c r="G81" s="43"/>
+      <c r="H81" s="42"/>
+      <c r="I81" s="43"/>
+      <c r="J81" s="43"/>
+      <c r="K81" s="43"/>
+      <c r="L81" s="43"/>
+    </row>
+    <row r="82" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B82" s="25"/>
+      <c r="C82" s="36"/>
+      <c r="D82" s="9"/>
+      <c r="E82" s="10"/>
+      <c r="F82" s="10"/>
+      <c r="G82" s="10"/>
+      <c r="H82" s="10"/>
+      <c r="I82" s="10"/>
+      <c r="J82" s="10"/>
+      <c r="K82" s="10"/>
+      <c r="L82" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4784,7 +4845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L80"/>
+  <dimension ref="A1:L81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -4809,10 +4870,10 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="71"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="65"/>
     </row>
     <row r="2" spans="1:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -4822,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="11"/>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="51" t="s">
         <v>267</v>
       </c>
       <c r="G2" s="12"/>
@@ -4840,7 +4901,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="13"/>
-      <c r="F3" s="53" t="s">
+      <c r="F3" s="52" t="s">
         <v>268</v>
       </c>
       <c r="G3" s="13"/>
@@ -4848,7 +4909,7 @@
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
-      <c r="L3" s="72"/>
+      <c r="L3" s="66"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -4858,7 +4919,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="13"/>
-      <c r="F4" s="53" t="s">
+      <c r="F4" s="52" t="s">
         <v>268</v>
       </c>
       <c r="G4" s="14"/>
@@ -4866,7 +4927,7 @@
       <c r="I4" s="7"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
-      <c r="L4" s="73"/>
+      <c r="L4" s="67"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -4876,7 +4937,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="13"/>
-      <c r="F5" s="54" t="s">
+      <c r="F5" s="53" t="s">
         <v>5</v>
       </c>
       <c r="G5" s="15"/>
@@ -4884,7 +4945,7 @@
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
-      <c r="L5" s="73"/>
+      <c r="L5" s="67"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -4898,7 +4959,7 @@
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
-      <c r="L6" s="73"/>
+      <c r="L6" s="67"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -4912,7 +4973,7 @@
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
-      <c r="L7" s="73"/>
+      <c r="L7" s="67"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -4926,7 +4987,7 @@
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
-      <c r="L8" s="73"/>
+      <c r="L8" s="67"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -4955,7 +5016,7 @@
         <v>271</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="K9" s="30" t="s">
         <v>274</v>
@@ -4964,17 +5025,17 @@
         <v>273</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="61" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A10" s="59"/>
+    <row r="10" spans="1:12" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A10" s="58"/>
       <c r="B10" s="45">
-        <f t="shared" ref="B10:B19" si="0">ROW(B10) - ROW($B$9)</f>
+        <f t="shared" ref="B10:B21" si="0">ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
       <c r="C10" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="74" t="s">
-        <v>275</v>
+      <c r="D10" s="62" t="s">
+        <v>316</v>
       </c>
       <c r="E10" s="47" t="s">
         <v>60</v>
@@ -4992,52 +5053,52 @@
         <v>242</v>
       </c>
       <c r="J10" s="37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K10" s="37">
-        <f t="shared" ref="K10:K73" si="1">J10*2</f>
-        <v>16</v>
-      </c>
-      <c r="L10" s="60"/>
-    </row>
-    <row r="11" spans="1:12" s="61" customFormat="1" ht="84" x14ac:dyDescent="0.25">
-      <c r="A11" s="59"/>
-      <c r="B11" s="45">
-        <f>ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="K10:K71" si="1">J10*2</f>
+        <v>14</v>
+      </c>
+      <c r="L10" s="59"/>
+    </row>
+    <row r="11" spans="1:12" s="60" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A11" s="58"/>
+      <c r="B11" s="44">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C11" s="49" t="s">
+      <c r="C11" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="75" t="s">
-        <v>276</v>
-      </c>
-      <c r="E11" s="47" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11" s="47" t="s">
-        <v>122</v>
-      </c>
-      <c r="G11" s="47" t="s">
-        <v>156</v>
-      </c>
-      <c r="H11" s="47" t="s">
+      <c r="D11" s="63" t="s">
+        <v>317</v>
+      </c>
+      <c r="E11" s="37" t="s">
+        <v>318</v>
+      </c>
+      <c r="F11" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="G11" s="37" t="s">
+        <v>319</v>
+      </c>
+      <c r="H11" s="37" t="s">
         <v>205</v>
       </c>
-      <c r="I11" s="47" t="s">
+      <c r="I11" s="37" t="s">
         <v>241</v>
       </c>
       <c r="J11" s="47">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="K11" s="37">
         <f t="shared" si="1"/>
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="L11" s="47"/>
     </row>
-    <row r="12" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="59"/>
+    <row r="12" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="58"/>
       <c r="B12" s="44">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -5045,8 +5106,8 @@
       <c r="C12" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="74" t="s">
-        <v>277</v>
+      <c r="D12" s="62" t="s">
+        <v>275</v>
       </c>
       <c r="E12" s="37" t="s">
         <v>58</v>
@@ -5070,82 +5131,82 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L12" s="55"/>
-    </row>
-    <row r="13" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="59"/>
-      <c r="B13" s="44">
+      <c r="L12" s="54"/>
+    </row>
+    <row r="13" spans="1:12" s="60" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A13" s="58"/>
+      <c r="B13" s="45">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="48" t="s">
+      <c r="C13" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="74" t="s">
-        <v>278</v>
-      </c>
-      <c r="E13" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="F13" s="37" t="s">
-        <v>269</v>
-      </c>
-      <c r="G13" s="37" t="s">
-        <v>123</v>
-      </c>
-      <c r="H13" s="37" t="s">
-        <v>206</v>
-      </c>
-      <c r="I13" s="37" t="s">
-        <v>243</v>
-      </c>
-      <c r="J13" s="37">
-        <v>2</v>
+      <c r="D13" s="63" t="s">
+        <v>320</v>
+      </c>
+      <c r="E13" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G13" s="47" t="s">
+        <v>156</v>
+      </c>
+      <c r="H13" s="47" t="s">
+        <v>205</v>
+      </c>
+      <c r="I13" s="47" t="s">
+        <v>241</v>
+      </c>
+      <c r="J13" s="47">
+        <v>18</v>
       </c>
       <c r="K13" s="37">
         <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="L13" s="55"/>
-    </row>
-    <row r="14" spans="1:12" s="61" customFormat="1" ht="72" x14ac:dyDescent="0.25">
-      <c r="A14" s="59"/>
-      <c r="B14" s="45">
+        <v>36</v>
+      </c>
+      <c r="L13" s="54"/>
+    </row>
+    <row r="14" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="58"/>
+      <c r="B14" s="44">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C14" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="75" t="s">
-        <v>279</v>
-      </c>
-      <c r="E14" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="F14" s="47" t="s">
-        <v>119</v>
-      </c>
-      <c r="G14" s="47" t="s">
-        <v>154</v>
-      </c>
-      <c r="H14" s="47" t="s">
-        <v>205</v>
-      </c>
-      <c r="I14" s="47" t="s">
-        <v>240</v>
-      </c>
-      <c r="J14" s="47">
-        <v>22</v>
+      <c r="D14" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="E14" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>269</v>
+      </c>
+      <c r="G14" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="H14" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="I14" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="J14" s="37">
+        <v>2</v>
       </c>
       <c r="K14" s="37">
         <f t="shared" si="1"/>
-        <v>44</v>
-      </c>
-      <c r="L14" s="55"/>
-    </row>
-    <row r="15" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="59"/>
+        <v>4</v>
+      </c>
+      <c r="L14" s="54"/>
+    </row>
+    <row r="15" spans="1:12" s="60" customFormat="1" ht="72" x14ac:dyDescent="0.25">
+      <c r="A15" s="58"/>
       <c r="B15" s="45">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -5153,35 +5214,35 @@
       <c r="C15" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="74" t="s">
-        <v>280</v>
+      <c r="D15" s="63" t="s">
+        <v>277</v>
       </c>
       <c r="E15" s="47" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F15" s="47" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="G15" s="47" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H15" s="47" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I15" s="47" t="s">
-        <v>243</v>
-      </c>
-      <c r="J15" s="37">
-        <v>1</v>
+        <v>240</v>
+      </c>
+      <c r="J15" s="47">
+        <v>22</v>
       </c>
       <c r="K15" s="37">
         <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="L15" s="55"/>
-    </row>
-    <row r="16" spans="1:12" s="61" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A16" s="59"/>
+        <v>44</v>
+      </c>
+      <c r="L15" s="54"/>
+    </row>
+    <row r="16" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="58"/>
       <c r="B16" s="45">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -5189,71 +5250,71 @@
       <c r="C16" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="75" t="s">
-        <v>281</v>
+      <c r="D16" s="62" t="s">
+        <v>278</v>
       </c>
       <c r="E16" s="47" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F16" s="47" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G16" s="47" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H16" s="47" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I16" s="47" t="s">
-        <v>244</v>
-      </c>
-      <c r="J16" s="47">
-        <v>6</v>
+        <v>243</v>
+      </c>
+      <c r="J16" s="37">
+        <v>1</v>
       </c>
       <c r="K16" s="37">
         <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="L16" s="55"/>
-    </row>
-    <row r="17" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="59"/>
-      <c r="B17" s="44">
+        <v>2</v>
+      </c>
+      <c r="L16" s="54"/>
+    </row>
+    <row r="17" spans="1:12" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A17" s="58"/>
+      <c r="B17" s="45">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C17" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="74" t="s">
-        <v>282</v>
-      </c>
-      <c r="E17" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="F17" s="37" t="s">
-        <v>122</v>
-      </c>
-      <c r="G17" s="37" t="s">
-        <v>338</v>
-      </c>
-      <c r="H17" s="37" t="s">
-        <v>208</v>
-      </c>
-      <c r="I17" s="37" t="s">
-        <v>245</v>
-      </c>
-      <c r="J17" s="37">
-        <v>3</v>
+      <c r="D17" s="63" t="s">
+        <v>279</v>
+      </c>
+      <c r="E17" s="47" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="G17" s="47" t="s">
+        <v>158</v>
+      </c>
+      <c r="H17" s="47" t="s">
+        <v>205</v>
+      </c>
+      <c r="I17" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="J17" s="47">
+        <v>6</v>
       </c>
       <c r="K17" s="37">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="L17" s="55"/>
-    </row>
-    <row r="18" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="59"/>
+        <v>12</v>
+      </c>
+      <c r="L17" s="54"/>
+    </row>
+    <row r="18" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="58"/>
       <c r="B18" s="44">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -5261,23 +5322,23 @@
       <c r="C18" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="74" t="s">
-        <v>283</v>
+      <c r="D18" s="62" t="s">
+        <v>280</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>119</v>
-      </c>
-      <c r="G18" s="37" t="s">
-        <v>152</v>
+        <v>122</v>
+      </c>
+      <c r="G18" s="55" t="s">
+        <v>321</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="J18" s="37">
         <v>3</v>
@@ -5286,458 +5347,458 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L18" s="55"/>
-    </row>
-    <row r="19" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="59"/>
-      <c r="B19" s="44">
+      <c r="L18" s="54"/>
+    </row>
+    <row r="19" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="58"/>
+      <c r="B19" s="45">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C19" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="75" t="s">
-        <v>284</v>
-      </c>
-      <c r="E19" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="F19" s="37" t="s">
+      <c r="D19" s="63" t="s">
+        <v>322</v>
+      </c>
+      <c r="E19" s="47" t="s">
+        <v>323</v>
+      </c>
+      <c r="F19" s="47" t="s">
         <v>119</v>
       </c>
-      <c r="G19" s="37" t="s">
-        <v>159</v>
-      </c>
-      <c r="H19" s="37" t="s">
+      <c r="G19" s="47" t="s">
+        <v>324</v>
+      </c>
+      <c r="H19" s="47" t="s">
         <v>205</v>
       </c>
-      <c r="I19" s="37" t="s">
-        <v>246</v>
+      <c r="I19" s="47" t="s">
+        <v>242</v>
       </c>
       <c r="J19" s="47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K19" s="37">
         <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="L19" s="55"/>
-    </row>
-    <row r="20" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="59"/>
-      <c r="B20" s="44"/>
-      <c r="C20" s="48"/>
-      <c r="D20" s="74" t="s">
-        <v>285</v>
+        <v>2</v>
+      </c>
+      <c r="L19" s="54"/>
+    </row>
+    <row r="20" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="58"/>
+      <c r="B20" s="44">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C20" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="62" t="s">
+        <v>281</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>286</v>
+        <v>56</v>
       </c>
       <c r="F20" s="37" t="s">
         <v>119</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>287</v>
+        <v>152</v>
       </c>
       <c r="H20" s="37" t="s">
         <v>205</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>333</v>
+        <v>237</v>
       </c>
       <c r="J20" s="37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K20" s="37">
         <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="L20" s="55"/>
-    </row>
-    <row r="21" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="59"/>
-      <c r="B21" s="45">
-        <f t="shared" ref="B21:B78" si="2">ROW(B21) - ROW($B$9)</f>
+        <v>6</v>
+      </c>
+      <c r="L20" s="54"/>
+    </row>
+    <row r="21" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="58"/>
+      <c r="B21" s="44">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="C21" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="75" t="s">
-        <v>288</v>
-      </c>
-      <c r="E21" s="47" t="s">
+      <c r="D21" s="63" t="s">
+        <v>282</v>
+      </c>
+      <c r="E21" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="G21" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="H21" s="37" t="s">
+        <v>205</v>
+      </c>
+      <c r="I21" s="37" t="s">
+        <v>246</v>
+      </c>
+      <c r="J21" s="47">
+        <v>4</v>
+      </c>
+      <c r="K21" s="37">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="L21" s="54"/>
+    </row>
+    <row r="22" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="58"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="62" t="s">
+        <v>283</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>284</v>
+      </c>
+      <c r="F22" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="G22" s="37" t="s">
+        <v>285</v>
+      </c>
+      <c r="H22" s="37" t="s">
+        <v>205</v>
+      </c>
+      <c r="I22" s="37" t="s">
+        <v>315</v>
+      </c>
+      <c r="J22" s="37">
+        <v>1</v>
+      </c>
+      <c r="K22" s="37">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L22" s="54"/>
+    </row>
+    <row r="23" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="58"/>
+      <c r="B23" s="45">
+        <f t="shared" ref="B23:B79" si="2">ROW(B23) - ROW($B$9)</f>
+        <v>14</v>
+      </c>
+      <c r="C23" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="E23" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="F21" s="47" t="s">
+      <c r="F23" s="47" t="s">
         <v>119</v>
       </c>
-      <c r="G21" s="47" t="s">
+      <c r="G23" s="47" t="s">
         <v>153</v>
       </c>
-      <c r="H21" s="47" t="s">
+      <c r="H23" s="47" t="s">
         <v>205</v>
       </c>
-      <c r="I21" s="47" t="s">
+      <c r="I23" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="J21" s="47">
-        <v>1</v>
-      </c>
-      <c r="K21" s="37">
+      <c r="J23" s="47">
+        <v>1</v>
+      </c>
+      <c r="K23" s="37">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L21" s="55"/>
-    </row>
-    <row r="22" spans="1:12" s="61" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A22" s="59"/>
-      <c r="B22" s="45">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
-      <c r="C22" s="48" t="s">
+      <c r="L23" s="54"/>
+    </row>
+    <row r="24" spans="1:12" s="60" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A24" s="58"/>
+      <c r="B24" s="45">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="C24" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="75" t="s">
+      <c r="D24" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="E22" s="47" t="s">
+      <c r="E24" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="47" t="s">
+      <c r="F24" s="47" t="s">
         <v>125</v>
       </c>
-      <c r="G22" s="47" t="s">
+      <c r="G24" s="47" t="s">
         <v>160</v>
       </c>
-      <c r="H22" s="47" t="s">
+      <c r="H24" s="47" t="s">
         <v>209</v>
       </c>
-      <c r="I22" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="J22" s="47">
+      <c r="I24" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="J24" s="47">
         <v>2</v>
       </c>
-      <c r="K22" s="37">
+      <c r="K24" s="37">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L22" s="55"/>
-    </row>
-    <row r="23" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="59"/>
-      <c r="B23" s="44">
-        <f>ROW(B23) - ROW($B$9)</f>
-        <v>14</v>
-      </c>
-      <c r="C23" s="48" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="74" t="s">
-        <v>28</v>
-      </c>
-      <c r="E23" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="F23" s="37" t="s">
-        <v>126</v>
-      </c>
-      <c r="G23" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="H23" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="I23" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="J23" s="37">
-        <v>1</v>
-      </c>
-      <c r="K23" s="37">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="L23" s="55"/>
-    </row>
-    <row r="24" spans="1:12" s="61" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A24" s="59"/>
-      <c r="B24" s="45">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-      <c r="C24" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="75" t="s">
-        <v>289</v>
-      </c>
-      <c r="E24" s="47" t="s">
-        <v>69</v>
-      </c>
-      <c r="F24" s="47" t="s">
-        <v>127</v>
-      </c>
-      <c r="G24" s="47" t="s">
-        <v>162</v>
-      </c>
-      <c r="H24" s="47" t="s">
-        <v>211</v>
-      </c>
-      <c r="I24" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="J24" s="47">
-        <v>3</v>
-      </c>
-      <c r="K24" s="37">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="L24" s="55"/>
-    </row>
-    <row r="25" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="59"/>
+      <c r="L24" s="54"/>
+    </row>
+    <row r="25" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="58"/>
       <c r="B25" s="44">
         <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="74" t="s">
-        <v>29</v>
+        <v>8</v>
+      </c>
+      <c r="D25" s="62" t="s">
+        <v>28</v>
       </c>
       <c r="E25" s="37" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F25" s="37" t="s">
         <v>126</v>
       </c>
       <c r="G25" s="37" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H25" s="37" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I25" s="47" t="s">
         <v>270</v>
       </c>
       <c r="J25" s="37">
+        <v>1</v>
+      </c>
+      <c r="K25" s="37">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="K25" s="37">
+      <c r="L25" s="54"/>
+    </row>
+    <row r="26" spans="1:12" s="60" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A26" s="58"/>
+      <c r="B26" s="45">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="C26" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="63" t="s">
+        <v>325</v>
+      </c>
+      <c r="E26" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" s="47" t="s">
+        <v>127</v>
+      </c>
+      <c r="G26" s="47" t="s">
+        <v>162</v>
+      </c>
+      <c r="H26" s="47" t="s">
+        <v>211</v>
+      </c>
+      <c r="I26" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="J26" s="47">
+        <v>2</v>
+      </c>
+      <c r="K26" s="37">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L25" s="55"/>
-    </row>
-    <row r="26" spans="1:12" s="61" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A26" s="59"/>
-      <c r="B26" s="45">
-        <f t="shared" si="2"/>
-        <v>17</v>
-      </c>
-      <c r="C26" s="49" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="75" t="s">
-        <v>30</v>
-      </c>
-      <c r="E26" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="F26" s="47" t="s">
-        <v>128</v>
-      </c>
-      <c r="G26" s="47" t="s">
-        <v>164</v>
-      </c>
-      <c r="H26" s="47" t="s">
-        <v>213</v>
-      </c>
-      <c r="I26" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="J26" s="47">
-        <v>1</v>
-      </c>
-      <c r="K26" s="37">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="L26" s="55"/>
-    </row>
-    <row r="27" spans="1:12" s="61" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A27" s="59"/>
+      <c r="L26" s="54"/>
+    </row>
+    <row r="27" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="58"/>
       <c r="B27" s="44">
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
       <c r="C27" s="48" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="74" t="s">
-        <v>290</v>
+        <v>9</v>
+      </c>
+      <c r="D27" s="62" t="s">
+        <v>29</v>
       </c>
       <c r="E27" s="37" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F27" s="37" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G27" s="37" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H27" s="37" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="I27" s="47" t="s">
         <v>270</v>
       </c>
       <c r="J27" s="37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K27" s="37">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="L27" s="55"/>
-    </row>
-    <row r="28" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="59"/>
+        <v>4</v>
+      </c>
+      <c r="L27" s="54"/>
+    </row>
+    <row r="28" spans="1:12" s="60" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A28" s="58"/>
       <c r="B28" s="45">
         <f t="shared" si="2"/>
         <v>19</v>
       </c>
       <c r="C28" s="49" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" s="75" t="s">
-        <v>291</v>
+        <v>10</v>
+      </c>
+      <c r="D28" s="63" t="s">
+        <v>30</v>
       </c>
       <c r="E28" s="47" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F28" s="47" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G28" s="47" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H28" s="47" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I28" s="47" t="s">
         <v>270</v>
       </c>
       <c r="J28" s="47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K28" s="37">
         <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="L28" s="55"/>
-    </row>
-    <row r="29" spans="1:12" s="61" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A29" s="59"/>
+        <v>2</v>
+      </c>
+      <c r="L28" s="54"/>
+    </row>
+    <row r="29" spans="1:12" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A29" s="58"/>
       <c r="B29" s="44">
         <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
       <c r="C29" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="D29" s="74" t="s">
-        <v>31</v>
+        <v>11</v>
+      </c>
+      <c r="D29" s="62" t="s">
+        <v>326</v>
       </c>
       <c r="E29" s="37" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F29" s="37" t="s">
-        <v>269</v>
+        <v>129</v>
       </c>
       <c r="G29" s="37" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H29" s="37" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="I29" s="47" t="s">
         <v>270</v>
       </c>
       <c r="J29" s="37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K29" s="37">
         <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="L29" s="55"/>
-    </row>
-    <row r="30" spans="1:12" s="61" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A30" s="59"/>
+        <v>6</v>
+      </c>
+      <c r="L29" s="54"/>
+    </row>
+    <row r="30" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="58"/>
       <c r="B30" s="45">
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="C30" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" s="75" t="s">
-        <v>32</v>
+        <v>11</v>
+      </c>
+      <c r="D30" s="63" t="s">
+        <v>327</v>
       </c>
       <c r="E30" s="47" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F30" s="47" t="s">
-        <v>269</v>
+        <v>130</v>
       </c>
       <c r="G30" s="47" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H30" s="47" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I30" s="47" t="s">
         <v>270</v>
       </c>
       <c r="J30" s="47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K30" s="37">
         <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="L30" s="55"/>
-    </row>
-    <row r="31" spans="1:12" s="61" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A31" s="59"/>
+        <v>8</v>
+      </c>
+      <c r="L30" s="54"/>
+    </row>
+    <row r="31" spans="1:12" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A31" s="58"/>
       <c r="B31" s="44">
         <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
       <c r="C31" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="D31" s="74" t="s">
-        <v>33</v>
+        <v>12</v>
+      </c>
+      <c r="D31" s="62" t="s">
+        <v>31</v>
       </c>
       <c r="E31" s="37" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F31" s="37" t="s">
         <v>269</v>
       </c>
       <c r="G31" s="37" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H31" s="37" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I31" s="47" t="s">
         <v>270</v>
@@ -5749,10 +5810,10 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L31" s="55"/>
-    </row>
-    <row r="32" spans="1:12" s="61" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A32" s="59"/>
+      <c r="L31" s="54"/>
+    </row>
+    <row r="32" spans="1:12" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A32" s="58"/>
       <c r="B32" s="45">
         <f t="shared" si="2"/>
         <v>23</v>
@@ -5760,203 +5821,203 @@
       <c r="C32" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="D32" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="E32" s="57" t="s">
-        <v>77</v>
-      </c>
-      <c r="F32" s="57" t="s">
+      <c r="D32" s="63" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="F32" s="47" t="s">
         <v>269</v>
       </c>
-      <c r="G32" s="57" t="s">
-        <v>131</v>
-      </c>
-      <c r="H32" s="57" t="s">
-        <v>218</v>
-      </c>
-      <c r="I32" s="57" t="s">
-        <v>247</v>
-      </c>
-      <c r="J32" s="57">
+      <c r="G32" s="47" t="s">
+        <v>168</v>
+      </c>
+      <c r="H32" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="I32" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="J32" s="47">
         <v>1</v>
       </c>
       <c r="K32" s="37">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L32" s="55"/>
-    </row>
-    <row r="33" spans="1:12" s="61" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A33" s="59"/>
+      <c r="L32" s="54"/>
+    </row>
+    <row r="33" spans="1:12" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A33" s="58"/>
       <c r="B33" s="44">
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
       <c r="C33" s="48" t="s">
-        <v>15</v>
-      </c>
-      <c r="D33" s="74" t="s">
-        <v>35</v>
+        <v>14</v>
+      </c>
+      <c r="D33" s="62" t="s">
+        <v>33</v>
       </c>
       <c r="E33" s="37" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>132</v>
+        <v>269</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>337</v>
+        <v>169</v>
       </c>
       <c r="H33" s="37" t="s">
-        <v>219</v>
-      </c>
-      <c r="I33" s="37" t="s">
+        <v>217</v>
+      </c>
+      <c r="I33" s="47" t="s">
         <v>270</v>
       </c>
       <c r="J33" s="37">
+        <v>1</v>
+      </c>
+      <c r="K33" s="37">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="K33" s="37">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="L33" s="55"/>
-    </row>
-    <row r="34" spans="1:12" s="61" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A34" s="59"/>
+      <c r="L33" s="54"/>
+    </row>
+    <row r="34" spans="1:12" s="60" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A34" s="58"/>
       <c r="B34" s="45">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
       <c r="C34" s="49" t="s">
-        <v>16</v>
-      </c>
-      <c r="D34" s="75" t="s">
-        <v>36</v>
-      </c>
-      <c r="E34" s="47" t="s">
-        <v>79</v>
-      </c>
-      <c r="F34" s="47" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="56" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" s="56" t="s">
+        <v>77</v>
+      </c>
+      <c r="F34" s="56" t="s">
         <v>269</v>
       </c>
-      <c r="G34" s="47" t="s">
-        <v>170</v>
-      </c>
-      <c r="H34" s="47" t="s">
-        <v>220</v>
-      </c>
-      <c r="I34" s="47" t="s">
-        <v>248</v>
-      </c>
-      <c r="J34" s="47">
+      <c r="G34" s="56" t="s">
+        <v>131</v>
+      </c>
+      <c r="H34" s="56" t="s">
+        <v>218</v>
+      </c>
+      <c r="I34" s="56" t="s">
+        <v>247</v>
+      </c>
+      <c r="J34" s="56">
         <v>1</v>
       </c>
       <c r="K34" s="37">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L34" s="55"/>
-    </row>
-    <row r="35" spans="1:12" s="61" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A35" s="59"/>
+      <c r="L34" s="54"/>
+    </row>
+    <row r="35" spans="1:12" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A35" s="58"/>
       <c r="B35" s="44">
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
       <c r="C35" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="62" t="s">
+        <v>35</v>
+      </c>
+      <c r="E35" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="F35" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="G35" s="55">
+        <v>61300211121</v>
+      </c>
+      <c r="H35" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="I35" s="37" t="s">
+        <v>270</v>
+      </c>
+      <c r="J35" s="37">
+        <v>2</v>
+      </c>
+      <c r="K35" s="37">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L35" s="54"/>
+    </row>
+    <row r="36" spans="1:12" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A36" s="58"/>
+      <c r="B36" s="45">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="C36" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="D35" s="74" t="s">
-        <v>37</v>
-      </c>
-      <c r="E35" s="37" t="s">
-        <v>80</v>
-      </c>
-      <c r="F35" s="37" t="s">
+      <c r="D36" s="63" t="s">
+        <v>36</v>
+      </c>
+      <c r="E36" s="47" t="s">
+        <v>79</v>
+      </c>
+      <c r="F36" s="47" t="s">
         <v>269</v>
       </c>
-      <c r="G35" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="H35" s="37" t="s">
+      <c r="G36" s="47" t="s">
+        <v>170</v>
+      </c>
+      <c r="H36" s="47" t="s">
         <v>220</v>
       </c>
-      <c r="I35" s="37" t="s">
-        <v>249</v>
-      </c>
-      <c r="J35" s="37">
-        <v>1</v>
-      </c>
-      <c r="K35" s="37">
+      <c r="I36" s="47" t="s">
+        <v>248</v>
+      </c>
+      <c r="J36" s="47">
+        <v>1</v>
+      </c>
+      <c r="K36" s="37">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L35" s="55"/>
-    </row>
-    <row r="36" spans="1:12" s="61" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A36" s="59"/>
-      <c r="B36" s="45">
-        <f t="shared" si="2"/>
-        <v>27</v>
-      </c>
-      <c r="C36" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="D36" s="75" t="s">
-        <v>38</v>
-      </c>
-      <c r="E36" s="47" t="s">
-        <v>81</v>
-      </c>
-      <c r="F36" s="47" t="s">
-        <v>133</v>
-      </c>
-      <c r="G36" s="47" t="s">
-        <v>172</v>
-      </c>
-      <c r="H36" s="47" t="s">
-        <v>221</v>
-      </c>
-      <c r="I36" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="J36" s="47">
-        <v>1</v>
-      </c>
-      <c r="K36" s="37">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="L36" s="55"/>
-    </row>
-    <row r="37" spans="1:12" s="61" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A37" s="59"/>
+      <c r="L36" s="54"/>
+    </row>
+    <row r="37" spans="1:12" s="60" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A37" s="58"/>
       <c r="B37" s="44">
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
       <c r="C37" s="48" t="s">
-        <v>17</v>
-      </c>
-      <c r="D37" s="74" t="s">
-        <v>39</v>
+        <v>16</v>
+      </c>
+      <c r="D37" s="62" t="s">
+        <v>37</v>
       </c>
       <c r="E37" s="37" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F37" s="37" t="s">
-        <v>133</v>
+        <v>269</v>
       </c>
       <c r="G37" s="37" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H37" s="37" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I37" s="37" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="J37" s="37">
         <v>1</v>
@@ -5965,10 +6026,10 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L37" s="55"/>
-    </row>
-    <row r="38" spans="1:12" s="61" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A38" s="59"/>
+      <c r="L37" s="54"/>
+    </row>
+    <row r="38" spans="1:12" s="60" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A38" s="58"/>
       <c r="B38" s="45">
         <f t="shared" si="2"/>
         <v>29</v>
@@ -5976,22 +6037,22 @@
       <c r="C38" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="75" t="s">
-        <v>40</v>
+      <c r="D38" s="63" t="s">
+        <v>38</v>
       </c>
       <c r="E38" s="47" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F38" s="47" t="s">
         <v>133</v>
       </c>
       <c r="G38" s="47" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H38" s="47" t="s">
         <v>221</v>
       </c>
-      <c r="I38" s="37" t="s">
+      <c r="I38" s="47" t="s">
         <v>270</v>
       </c>
       <c r="J38" s="47">
@@ -6001,31 +6062,31 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L38" s="55"/>
-    </row>
-    <row r="39" spans="1:12" s="61" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A39" s="59"/>
+      <c r="L38" s="54"/>
+    </row>
+    <row r="39" spans="1:12" s="60" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A39" s="58"/>
       <c r="B39" s="44">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
       <c r="C39" s="48" t="s">
-        <v>18</v>
-      </c>
-      <c r="D39" s="74" t="s">
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="D39" s="62" t="s">
+        <v>39</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H39" s="37" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I39" s="37" t="s">
         <v>270</v>
@@ -6037,67 +6098,67 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L39" s="55"/>
-    </row>
-    <row r="40" spans="1:12" s="61" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A40" s="59"/>
+      <c r="L39" s="54"/>
+    </row>
+    <row r="40" spans="1:12" s="60" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A40" s="58"/>
       <c r="B40" s="45">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="C40" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" s="57" t="s">
-        <v>292</v>
-      </c>
-      <c r="E40" s="57" t="s">
-        <v>85</v>
-      </c>
-      <c r="F40" s="57" t="s">
-        <v>269</v>
-      </c>
-      <c r="G40" s="57" t="s">
-        <v>270</v>
-      </c>
-      <c r="H40" s="57" t="s">
-        <v>270</v>
-      </c>
-      <c r="I40" s="56" t="s">
-        <v>270</v>
-      </c>
-      <c r="J40" s="57">
-        <v>14</v>
+        <v>17</v>
+      </c>
+      <c r="D40" s="63" t="s">
+        <v>40</v>
+      </c>
+      <c r="E40" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="F40" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="G40" s="47" t="s">
+        <v>174</v>
+      </c>
+      <c r="H40" s="47" t="s">
+        <v>221</v>
+      </c>
+      <c r="I40" s="37" t="s">
+        <v>270</v>
+      </c>
+      <c r="J40" s="47">
+        <v>1</v>
       </c>
       <c r="K40" s="37">
         <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-      <c r="L40" s="55"/>
-    </row>
-    <row r="41" spans="1:12" s="61" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A41" s="59"/>
+        <v>2</v>
+      </c>
+      <c r="L40" s="54"/>
+    </row>
+    <row r="41" spans="1:12" s="60" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A41" s="58"/>
       <c r="B41" s="44">
         <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
       <c r="C41" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" s="74" t="s">
-        <v>42</v>
+        <v>18</v>
+      </c>
+      <c r="D41" s="62" t="s">
+        <v>41</v>
       </c>
       <c r="E41" s="37" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F41" s="37" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G41" s="37" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H41" s="37" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I41" s="37" t="s">
         <v>270</v>
@@ -6109,154 +6170,154 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L41" s="55"/>
-    </row>
-    <row r="42" spans="1:12" s="61" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A42" s="59"/>
+      <c r="L41" s="54"/>
+    </row>
+    <row r="42" spans="1:12" s="60" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A42" s="58"/>
       <c r="B42" s="45">
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
       <c r="C42" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="D42" s="75" t="s">
-        <v>293</v>
-      </c>
-      <c r="E42" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="F42" s="47" t="s">
-        <v>136</v>
-      </c>
-      <c r="G42" s="47" t="s">
-        <v>177</v>
-      </c>
-      <c r="H42" s="47" t="s">
-        <v>224</v>
-      </c>
-      <c r="I42" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="J42" s="47">
-        <v>2</v>
+        <v>19</v>
+      </c>
+      <c r="D42" s="56" t="s">
+        <v>328</v>
+      </c>
+      <c r="E42" s="56" t="s">
+        <v>85</v>
+      </c>
+      <c r="F42" s="56" t="s">
+        <v>269</v>
+      </c>
+      <c r="G42" s="56" t="s">
+        <v>270</v>
+      </c>
+      <c r="H42" s="56" t="s">
+        <v>270</v>
+      </c>
+      <c r="I42" s="55" t="s">
+        <v>270</v>
+      </c>
+      <c r="J42" s="56">
+        <v>15</v>
       </c>
       <c r="K42" s="37">
         <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="L42" s="55"/>
-    </row>
-    <row r="43" spans="1:12" s="61" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A43" s="59"/>
+        <v>30</v>
+      </c>
+      <c r="L42" s="54"/>
+    </row>
+    <row r="43" spans="1:12" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A43" s="58"/>
       <c r="B43" s="44">
-        <f t="shared" si="2"/>
+        <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
       </c>
       <c r="C43" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="D43" s="74" t="s">
+      <c r="D43" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="E43" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="F43" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G43" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="H43" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="I43" s="37" t="s">
+        <v>270</v>
+      </c>
+      <c r="J43" s="37">
+        <v>1</v>
+      </c>
+      <c r="K43" s="37">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L43" s="54"/>
+    </row>
+    <row r="44" spans="1:12" s="60" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A44" s="58"/>
+      <c r="B44" s="45">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+      <c r="C44" s="49" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" s="63" t="s">
+        <v>329</v>
+      </c>
+      <c r="E44" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="F44" s="47" t="s">
+        <v>136</v>
+      </c>
+      <c r="G44" s="47" t="s">
+        <v>177</v>
+      </c>
+      <c r="H44" s="47" t="s">
+        <v>224</v>
+      </c>
+      <c r="I44" s="37" t="s">
+        <v>270</v>
+      </c>
+      <c r="J44" s="47">
+        <v>3</v>
+      </c>
+      <c r="K44" s="37">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L44" s="54"/>
+    </row>
+    <row r="45" spans="1:12" s="60" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A45" s="58"/>
+      <c r="B45" s="44">
+        <f t="shared" si="2"/>
+        <v>36</v>
+      </c>
+      <c r="C45" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="E43" s="37" t="s">
+      <c r="E45" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="F43" s="37" t="s">
+      <c r="F45" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="G43" s="37" t="s">
+      <c r="G45" s="37" t="s">
         <v>178</v>
       </c>
-      <c r="H43" s="37" t="s">
+      <c r="H45" s="37" t="s">
         <v>225</v>
       </c>
-      <c r="I43" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="J43" s="37">
+      <c r="I45" s="37" t="s">
+        <v>270</v>
+      </c>
+      <c r="J45" s="37">
         <v>4</v>
       </c>
-      <c r="K43" s="37">
+      <c r="K45" s="37">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="L43" s="55"/>
-    </row>
-    <row r="44" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="59"/>
-      <c r="B44" s="45">
-        <f t="shared" si="2"/>
-        <v>35</v>
-      </c>
-      <c r="C44" s="49" t="s">
-        <v>21</v>
-      </c>
-      <c r="D44" s="75" t="s">
-        <v>294</v>
-      </c>
-      <c r="E44" s="47" t="s">
-        <v>295</v>
-      </c>
-      <c r="F44" s="47" t="s">
-        <v>296</v>
-      </c>
-      <c r="G44" s="47" t="s">
-        <v>297</v>
-      </c>
-      <c r="H44" s="47" t="s">
-        <v>205</v>
-      </c>
-      <c r="I44" s="47" t="s">
-        <v>334</v>
-      </c>
-      <c r="J44" s="47">
-        <v>1</v>
-      </c>
-      <c r="K44" s="37">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="L44" s="55"/>
-    </row>
-    <row r="45" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="59"/>
-      <c r="B45" s="45">
-        <f>ROW(B45) - ROW($B$9)</f>
-        <v>36</v>
-      </c>
-      <c r="C45" s="49" t="s">
-        <v>21</v>
-      </c>
-      <c r="D45" s="75" t="s">
-        <v>298</v>
-      </c>
-      <c r="E45" s="47" t="s">
-        <v>89</v>
-      </c>
-      <c r="F45" s="47" t="s">
-        <v>138</v>
-      </c>
-      <c r="G45" s="47" t="s">
-        <v>179</v>
-      </c>
-      <c r="H45" s="47" t="s">
-        <v>205</v>
-      </c>
-      <c r="I45" s="47" t="s">
-        <v>250</v>
-      </c>
-      <c r="J45" s="47">
-        <v>4</v>
-      </c>
-      <c r="K45" s="37">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="L45" s="55"/>
-    </row>
-    <row r="46" spans="1:12" s="61" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A46" s="59"/>
+      <c r="L45" s="54"/>
+    </row>
+    <row r="46" spans="1:12" s="60" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A46" s="58"/>
       <c r="B46" s="44">
         <f t="shared" si="2"/>
         <v>37</v>
@@ -6264,8 +6325,8 @@
       <c r="C46" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D46" s="75" t="s">
-        <v>299</v>
+      <c r="D46" s="63" t="s">
+        <v>330</v>
       </c>
       <c r="E46" s="37" t="s">
         <v>90</v>
@@ -6283,88 +6344,88 @@
         <v>251</v>
       </c>
       <c r="J46" s="37">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K46" s="37">
         <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-      <c r="L46" s="55"/>
-    </row>
-    <row r="47" spans="1:12" s="61" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A47" s="59"/>
-      <c r="B47" s="44">
+        <v>28</v>
+      </c>
+      <c r="L46" s="54"/>
+    </row>
+    <row r="47" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="58"/>
+      <c r="B47" s="45">
         <f t="shared" si="2"/>
         <v>38</v>
       </c>
-      <c r="C47" s="48" t="s">
+      <c r="C47" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D47" s="74" t="s">
-        <v>300</v>
-      </c>
-      <c r="E47" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="F47" s="37" t="s">
-        <v>139</v>
-      </c>
-      <c r="G47" s="37" t="s">
-        <v>181</v>
-      </c>
-      <c r="H47" s="37" t="s">
-        <v>226</v>
-      </c>
-      <c r="I47" s="37" t="s">
-        <v>252</v>
-      </c>
-      <c r="J47" s="37">
+      <c r="D47" s="62" t="s">
+        <v>331</v>
+      </c>
+      <c r="E47" s="47" t="s">
+        <v>332</v>
+      </c>
+      <c r="F47" s="47" t="s">
+        <v>138</v>
+      </c>
+      <c r="G47" s="47" t="s">
+        <v>333</v>
+      </c>
+      <c r="H47" s="47" t="s">
+        <v>334</v>
+      </c>
+      <c r="I47" s="47" t="s">
+        <v>340</v>
+      </c>
+      <c r="J47" s="47">
         <v>1</v>
       </c>
       <c r="K47" s="37">
-        <f t="shared" si="1"/>
+        <f>J47*2</f>
         <v>2</v>
       </c>
-      <c r="L47" s="55"/>
-    </row>
-    <row r="48" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="59"/>
-      <c r="B48" s="44">
+      <c r="L47" s="54"/>
+    </row>
+    <row r="48" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="58"/>
+      <c r="B48" s="45">
         <f t="shared" si="2"/>
         <v>39</v>
       </c>
       <c r="C48" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D48" s="75" t="s">
-        <v>301</v>
-      </c>
-      <c r="E48" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="F48" s="37" t="s">
+      <c r="D48" s="63" t="s">
+        <v>287</v>
+      </c>
+      <c r="E48" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="F48" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="G48" s="37" t="s">
-        <v>184</v>
-      </c>
-      <c r="H48" s="37" t="s">
+      <c r="G48" s="47" t="s">
+        <v>179</v>
+      </c>
+      <c r="H48" s="47" t="s">
         <v>205</v>
       </c>
-      <c r="I48" s="37" t="s">
-        <v>255</v>
-      </c>
-      <c r="J48" s="37">
-        <v>1</v>
+      <c r="I48" s="47" t="s">
+        <v>250</v>
+      </c>
+      <c r="J48" s="47">
+        <v>4</v>
       </c>
       <c r="K48" s="37">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="L48" s="55"/>
-    </row>
-    <row r="49" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="59"/>
+        <f>J48*2</f>
+        <v>8</v>
+      </c>
+      <c r="L48" s="54"/>
+    </row>
+    <row r="49" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="58"/>
       <c r="B49" s="45">
         <f t="shared" si="2"/>
         <v>40</v>
@@ -6372,71 +6433,71 @@
       <c r="C49" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D49" s="74" t="s">
-        <v>302</v>
+      <c r="D49" s="62" t="s">
+        <v>335</v>
       </c>
       <c r="E49" s="47" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F49" s="47" t="s">
         <v>138</v>
       </c>
       <c r="G49" s="47" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H49" s="47" t="s">
         <v>205</v>
       </c>
       <c r="I49" s="47" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="J49" s="47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K49" s="37">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="L49" s="55"/>
-    </row>
-    <row r="50" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="59"/>
-      <c r="B50" s="45">
+        <f>J49*2</f>
+        <v>6</v>
+      </c>
+      <c r="L49" s="54"/>
+    </row>
+    <row r="50" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="58"/>
+      <c r="B50" s="44">
         <f t="shared" si="2"/>
         <v>41</v>
       </c>
       <c r="C50" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D50" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="E50" s="47" t="s">
-        <v>97</v>
-      </c>
-      <c r="F50" s="47" t="s">
+      <c r="D50" s="63" t="s">
+        <v>336</v>
+      </c>
+      <c r="E50" s="37" t="s">
+        <v>337</v>
+      </c>
+      <c r="F50" s="37" t="s">
         <v>138</v>
       </c>
-      <c r="G50" s="47" t="s">
-        <v>187</v>
-      </c>
-      <c r="H50" s="47" t="s">
+      <c r="G50" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="H50" s="37" t="s">
         <v>205</v>
       </c>
-      <c r="I50" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="J50" s="47">
+      <c r="I50" s="37" t="s">
+        <v>341</v>
+      </c>
+      <c r="J50" s="37">
         <v>1</v>
       </c>
       <c r="K50" s="37">
-        <f t="shared" si="1"/>
+        <f>J50*2</f>
         <v>2</v>
       </c>
-      <c r="L50" s="55"/>
-    </row>
-    <row r="51" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="59"/>
+      <c r="L50" s="54"/>
+    </row>
+    <row r="51" spans="1:12" s="60" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A51" s="58"/>
       <c r="B51" s="44">
         <f t="shared" si="2"/>
         <v>42</v>
@@ -6444,23 +6505,23 @@
       <c r="C51" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="D51" s="74" t="s">
-        <v>45</v>
+      <c r="D51" s="62" t="s">
+        <v>288</v>
       </c>
       <c r="E51" s="37" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="F51" s="37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G51" s="37" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="H51" s="37" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="I51" s="37" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="J51" s="37">
         <v>1</v>
@@ -6469,10 +6530,10 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L51" s="55"/>
-    </row>
-    <row r="52" spans="1:12" s="61" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A52" s="59"/>
+      <c r="L51" s="54"/>
+    </row>
+    <row r="52" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="58"/>
       <c r="B52" s="44">
         <f t="shared" si="2"/>
         <v>43</v>
@@ -6480,59 +6541,59 @@
       <c r="C52" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D52" s="75" t="s">
-        <v>303</v>
+      <c r="D52" s="63" t="s">
+        <v>289</v>
       </c>
       <c r="E52" s="37" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F52" s="37" t="s">
         <v>138</v>
       </c>
       <c r="G52" s="37" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H52" s="37" t="s">
         <v>205</v>
       </c>
       <c r="I52" s="37" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="J52" s="37">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K52" s="37">
         <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="L52" s="55"/>
-    </row>
-    <row r="53" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="59"/>
+        <v>2</v>
+      </c>
+      <c r="L52" s="54"/>
+    </row>
+    <row r="53" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="58"/>
       <c r="B53" s="45">
         <f t="shared" si="2"/>
         <v>44</v>
       </c>
-      <c r="C53" s="48" t="s">
+      <c r="C53" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D53" s="74" t="s">
-        <v>304</v>
+      <c r="D53" s="62" t="s">
+        <v>290</v>
       </c>
       <c r="E53" s="47" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F53" s="47" t="s">
         <v>138</v>
       </c>
       <c r="G53" s="47" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="H53" s="47" t="s">
         <v>205</v>
       </c>
       <c r="I53" s="47" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J53" s="47">
         <v>1</v>
@@ -6541,262 +6602,262 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L53" s="55"/>
-    </row>
-    <row r="54" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="59"/>
-      <c r="B54" s="44">
+      <c r="L53" s="54"/>
+    </row>
+    <row r="54" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="58"/>
+      <c r="B54" s="45">
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="C54" s="48" t="s">
+      <c r="C54" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D54" s="75" t="s">
-        <v>305</v>
-      </c>
-      <c r="E54" s="37" t="s">
-        <v>100</v>
-      </c>
-      <c r="F54" s="37" t="s">
+      <c r="D54" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="E54" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="F54" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="G54" s="37" t="s">
-        <v>190</v>
-      </c>
-      <c r="H54" s="37" t="s">
+      <c r="G54" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="H54" s="47" t="s">
         <v>205</v>
       </c>
-      <c r="I54" s="37" t="s">
-        <v>261</v>
-      </c>
-      <c r="J54" s="37">
+      <c r="I54" s="47" t="s">
+        <v>258</v>
+      </c>
+      <c r="J54" s="47">
+        <v>1</v>
+      </c>
+      <c r="K54" s="37">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="K54" s="37">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="L54" s="55"/>
-    </row>
-    <row r="55" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="59"/>
-      <c r="B55" s="45">
+      <c r="L54" s="54"/>
+    </row>
+    <row r="55" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="58"/>
+      <c r="B55" s="44">
         <f t="shared" si="2"/>
         <v>46</v>
       </c>
-      <c r="C55" s="49" t="s">
+      <c r="C55" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="D55" s="74" t="s">
-        <v>306</v>
-      </c>
-      <c r="E55" s="47" t="s">
-        <v>101</v>
-      </c>
-      <c r="F55" s="47" t="s">
+      <c r="D55" s="62" t="s">
+        <v>45</v>
+      </c>
+      <c r="E55" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="F55" s="37" t="s">
         <v>138</v>
       </c>
-      <c r="G55" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="H55" s="47" t="s">
+      <c r="G55" s="37" t="s">
+        <v>188</v>
+      </c>
+      <c r="H55" s="37" t="s">
         <v>205</v>
       </c>
-      <c r="I55" s="47" t="s">
-        <v>262</v>
-      </c>
-      <c r="J55" s="47">
+      <c r="I55" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J55" s="37">
         <v>1</v>
       </c>
       <c r="K55" s="37">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L55" s="55"/>
-    </row>
-    <row r="56" spans="1:12" s="61" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A56" s="59"/>
+      <c r="L55" s="54"/>
+    </row>
+    <row r="56" spans="1:12" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A56" s="58"/>
       <c r="B56" s="44">
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="C56" s="48" t="s">
+      <c r="C56" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D56" s="75" t="s">
-        <v>307</v>
+      <c r="D56" s="63" t="s">
+        <v>291</v>
       </c>
       <c r="E56" s="37" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F56" s="37" t="s">
         <v>138</v>
       </c>
       <c r="G56" s="37" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="H56" s="37" t="s">
         <v>205</v>
       </c>
       <c r="I56" s="37" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="J56" s="37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K56" s="37">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L56" s="55"/>
-    </row>
-    <row r="57" spans="1:12" s="61" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A57" s="59"/>
+        <v>12</v>
+      </c>
+      <c r="L56" s="54"/>
+    </row>
+    <row r="57" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="58"/>
       <c r="B57" s="45">
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="C57" s="49" t="s">
+      <c r="C57" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="D57" s="74" t="s">
-        <v>308</v>
+      <c r="D57" s="62" t="s">
+        <v>292</v>
       </c>
       <c r="E57" s="47" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F57" s="47" t="s">
         <v>138</v>
       </c>
       <c r="G57" s="47" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="H57" s="47" t="s">
         <v>205</v>
       </c>
       <c r="I57" s="47" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="J57" s="47">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K57" s="37">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L57" s="55"/>
-    </row>
-    <row r="58" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="59"/>
-      <c r="B58" s="45">
+        <v>2</v>
+      </c>
+      <c r="L57" s="54"/>
+    </row>
+    <row r="58" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="58"/>
+      <c r="B58" s="44">
         <f t="shared" si="2"/>
         <v>49</v>
       </c>
-      <c r="C58" s="49" t="s">
+      <c r="C58" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="D58" s="75" t="s">
-        <v>309</v>
-      </c>
-      <c r="E58" s="47" t="s">
-        <v>103</v>
-      </c>
-      <c r="F58" s="47" t="s">
+      <c r="D58" s="63" t="s">
+        <v>293</v>
+      </c>
+      <c r="E58" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="F58" s="37" t="s">
         <v>138</v>
       </c>
-      <c r="G58" s="47" t="s">
-        <v>193</v>
-      </c>
-      <c r="H58" s="47" t="s">
+      <c r="G58" s="37" t="s">
+        <v>190</v>
+      </c>
+      <c r="H58" s="37" t="s">
         <v>205</v>
       </c>
-      <c r="I58" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="J58" s="47">
+      <c r="I58" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="J58" s="37">
         <v>2</v>
       </c>
       <c r="K58" s="37">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L58" s="55"/>
-    </row>
-    <row r="59" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="59"/>
-      <c r="B59" s="44">
-        <f>ROW(B59) - ROW($B$9)</f>
+      <c r="L58" s="54"/>
+    </row>
+    <row r="59" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="58"/>
+      <c r="B59" s="45">
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="C59" s="48" t="s">
+      <c r="C59" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D59" s="37" t="s">
-        <v>310</v>
-      </c>
-      <c r="E59" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="F59" s="37" t="s">
+      <c r="D59" s="62" t="s">
+        <v>294</v>
+      </c>
+      <c r="E59" s="47" t="s">
+        <v>101</v>
+      </c>
+      <c r="F59" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="G59" s="37" t="s">
-        <v>182</v>
-      </c>
-      <c r="H59" s="37" t="s">
+      <c r="G59" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="H59" s="47" t="s">
         <v>205</v>
       </c>
-      <c r="I59" s="37" t="s">
-        <v>253</v>
-      </c>
-      <c r="J59" s="37">
+      <c r="I59" s="47" t="s">
+        <v>262</v>
+      </c>
+      <c r="J59" s="47">
+        <v>1</v>
+      </c>
+      <c r="K59" s="37">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="K59" s="37">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="L59" s="55"/>
-    </row>
-    <row r="60" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="59"/>
+      <c r="L59" s="54"/>
+    </row>
+    <row r="60" spans="1:12" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A60" s="58"/>
       <c r="B60" s="44">
-        <f>ROW(B60) - ROW($B$9)</f>
+        <f t="shared" si="2"/>
         <v>51</v>
       </c>
       <c r="C60" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="D60" s="74" t="s">
-        <v>311</v>
+      <c r="D60" s="63" t="s">
+        <v>295</v>
       </c>
       <c r="E60" s="37" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F60" s="37" t="s">
         <v>138</v>
       </c>
       <c r="G60" s="37" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H60" s="37" t="s">
         <v>205</v>
       </c>
       <c r="I60" s="37" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="J60" s="37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K60" s="37">
         <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="L60" s="55"/>
-    </row>
-    <row r="61" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="59"/>
+        <v>10</v>
+      </c>
+      <c r="L60" s="54"/>
+    </row>
+    <row r="61" spans="1:12" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A61" s="58"/>
       <c r="B61" s="45">
         <f t="shared" si="2"/>
         <v>52</v>
@@ -6804,359 +6865,359 @@
       <c r="C61" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D61" s="75" t="s">
-        <v>312</v>
+      <c r="D61" s="62" t="s">
+        <v>296</v>
       </c>
       <c r="E61" s="47" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="F61" s="47" t="s">
         <v>138</v>
       </c>
       <c r="G61" s="47" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="H61" s="47" t="s">
         <v>205</v>
       </c>
       <c r="I61" s="47" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="J61" s="47">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K61" s="37">
         <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L61" s="54"/>
+    </row>
+    <row r="62" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="58"/>
+      <c r="B62" s="45">
+        <f t="shared" si="2"/>
+        <v>53</v>
+      </c>
+      <c r="C62" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="D62" s="63" t="s">
+        <v>297</v>
+      </c>
+      <c r="E62" s="47" t="s">
+        <v>103</v>
+      </c>
+      <c r="F62" s="47" t="s">
+        <v>138</v>
+      </c>
+      <c r="G62" s="47" t="s">
+        <v>193</v>
+      </c>
+      <c r="H62" s="47" t="s">
+        <v>205</v>
+      </c>
+      <c r="I62" s="47" t="s">
+        <v>264</v>
+      </c>
+      <c r="J62" s="47">
         <v>2</v>
       </c>
-      <c r="L61" s="55"/>
-    </row>
-    <row r="62" spans="1:12" s="61" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A62" s="59"/>
-      <c r="B62" s="45">
-        <f t="shared" si="2"/>
-        <v>53</v>
-      </c>
-      <c r="C62" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="D62" s="57" t="s">
-        <v>313</v>
-      </c>
-      <c r="E62" s="57" t="s">
-        <v>106</v>
-      </c>
-      <c r="F62" s="57" t="s">
-        <v>269</v>
-      </c>
-      <c r="G62" s="57" t="s">
-        <v>140</v>
-      </c>
-      <c r="H62" s="57" t="s">
-        <v>270</v>
-      </c>
-      <c r="I62" s="58" t="s">
-        <v>270</v>
-      </c>
-      <c r="J62" s="57">
-        <v>10</v>
-      </c>
       <c r="K62" s="37">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="L62" s="55"/>
-    </row>
-    <row r="63" spans="1:12" s="61" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A63" s="59"/>
+        <v>4</v>
+      </c>
+      <c r="L62" s="54"/>
+    </row>
+    <row r="63" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="58"/>
       <c r="B63" s="44">
         <f>ROW(B63) - ROW($B$9)</f>
         <v>54</v>
       </c>
       <c r="C63" s="48" t="s">
+        <v>21</v>
+      </c>
+      <c r="D63" s="62" t="s">
+        <v>298</v>
+      </c>
+      <c r="E63" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="F63" s="37" t="s">
+        <v>138</v>
+      </c>
+      <c r="G63" s="37" t="s">
+        <v>194</v>
+      </c>
+      <c r="H63" s="37" t="s">
+        <v>205</v>
+      </c>
+      <c r="I63" s="37" t="s">
+        <v>265</v>
+      </c>
+      <c r="J63" s="37">
+        <v>4</v>
+      </c>
+      <c r="K63" s="37">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="L63" s="54"/>
+    </row>
+    <row r="64" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="58"/>
+      <c r="B64" s="45">
+        <f t="shared" si="2"/>
+        <v>55</v>
+      </c>
+      <c r="C64" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="D64" s="63" t="s">
+        <v>299</v>
+      </c>
+      <c r="E64" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="F64" s="47" t="s">
+        <v>138</v>
+      </c>
+      <c r="G64" s="47" t="s">
+        <v>195</v>
+      </c>
+      <c r="H64" s="47" t="s">
+        <v>205</v>
+      </c>
+      <c r="I64" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="J64" s="47">
+        <v>1</v>
+      </c>
+      <c r="K64" s="37">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L64" s="54"/>
+    </row>
+    <row r="65" spans="1:12" s="60" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A65" s="58"/>
+      <c r="B65" s="45">
+        <f t="shared" si="2"/>
+        <v>56</v>
+      </c>
+      <c r="C65" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="D65" s="56" t="s">
+        <v>300</v>
+      </c>
+      <c r="E65" s="56" t="s">
+        <v>106</v>
+      </c>
+      <c r="F65" s="56" t="s">
+        <v>269</v>
+      </c>
+      <c r="G65" s="56" t="s">
+        <v>140</v>
+      </c>
+      <c r="H65" s="56" t="s">
+        <v>270</v>
+      </c>
+      <c r="I65" s="57" t="s">
+        <v>270</v>
+      </c>
+      <c r="J65" s="56">
+        <v>10</v>
+      </c>
+      <c r="K65" s="56">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="L65" s="54"/>
+    </row>
+    <row r="66" spans="1:12" s="60" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A66" s="58"/>
+      <c r="B66" s="44">
+        <f>ROW(B66) - ROW($B$9)</f>
+        <v>57</v>
+      </c>
+      <c r="C66" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="D63" s="74" t="s">
-        <v>314</v>
-      </c>
-      <c r="E63" s="37" t="s">
+      <c r="D66" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="E66" s="37" t="s">
         <v>108</v>
-      </c>
-      <c r="F63" s="47" t="s">
-        <v>269</v>
-      </c>
-      <c r="G63" s="37" t="s">
-        <v>142</v>
-      </c>
-      <c r="H63" s="37" t="s">
-        <v>227</v>
-      </c>
-      <c r="I63" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="J63" s="37">
-        <v>2</v>
-      </c>
-      <c r="K63" s="37">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="L63" s="55"/>
-    </row>
-    <row r="64" spans="1:12" s="61" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A64" s="59"/>
-      <c r="B64" s="45">
-        <f>ROW(B64) - ROW($B$9)</f>
-        <v>55</v>
-      </c>
-      <c r="C64" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="D64" s="75" t="s">
-        <v>315</v>
-      </c>
-      <c r="E64" s="47" t="s">
-        <v>109</v>
-      </c>
-      <c r="F64" s="47" t="s">
-        <v>269</v>
-      </c>
-      <c r="G64" s="47" t="s">
-        <v>196</v>
-      </c>
-      <c r="H64" s="47" t="s">
-        <v>228</v>
-      </c>
-      <c r="I64" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="J64" s="47">
-        <v>1</v>
-      </c>
-      <c r="K64" s="37">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="L64" s="55"/>
-    </row>
-    <row r="65" spans="1:12" s="61" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A65" s="59"/>
-      <c r="B65" s="44">
-        <f>ROW(B65) - ROW($B$9)</f>
-        <v>56</v>
-      </c>
-      <c r="C65" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="D65" s="74" t="s">
-        <v>316</v>
-      </c>
-      <c r="E65" s="37" t="s">
-        <v>110</v>
-      </c>
-      <c r="F65" s="47" t="s">
-        <v>269</v>
-      </c>
-      <c r="G65" s="37" t="s">
-        <v>197</v>
-      </c>
-      <c r="H65" s="37" t="s">
-        <v>227</v>
-      </c>
-      <c r="I65" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="J65" s="37">
-        <v>4</v>
-      </c>
-      <c r="K65" s="37">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="L65" s="55"/>
-    </row>
-    <row r="66" spans="1:12" s="61" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A66" s="59"/>
-      <c r="B66" s="45">
-        <f t="shared" si="2"/>
-        <v>57</v>
-      </c>
-      <c r="C66" s="49" t="s">
-        <v>23</v>
-      </c>
-      <c r="D66" s="75" t="s">
-        <v>317</v>
-      </c>
-      <c r="E66" s="47" t="s">
-        <v>107</v>
       </c>
       <c r="F66" s="47" t="s">
         <v>269</v>
       </c>
-      <c r="G66" s="47" t="s">
+      <c r="G66" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="H66" s="37" t="s">
+        <v>227</v>
+      </c>
+      <c r="I66" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="J66" s="37">
+        <v>2</v>
+      </c>
+      <c r="K66" s="37">
+        <f>J66*2</f>
+        <v>4</v>
+      </c>
+      <c r="L66" s="54"/>
+    </row>
+    <row r="67" spans="1:12" s="60" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A67" s="58"/>
+      <c r="B67" s="45">
+        <f>ROW(B67) - ROW($B$9)</f>
+        <v>58</v>
+      </c>
+      <c r="C67" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="D67" s="47" t="s">
+        <v>302</v>
+      </c>
+      <c r="E67" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="F67" s="47" t="s">
+        <v>269</v>
+      </c>
+      <c r="G67" s="47" t="s">
+        <v>196</v>
+      </c>
+      <c r="H67" s="47" t="s">
+        <v>228</v>
+      </c>
+      <c r="I67" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="J67" s="47">
+        <v>1</v>
+      </c>
+      <c r="K67" s="37">
+        <f>J67*2</f>
+        <v>2</v>
+      </c>
+      <c r="L67" s="54"/>
+    </row>
+    <row r="68" spans="1:12" s="60" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A68" s="58"/>
+      <c r="B68" s="44">
+        <f>ROW(B68) - ROW($B$9)</f>
+        <v>59</v>
+      </c>
+      <c r="C68" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="D68" s="37" t="s">
+        <v>303</v>
+      </c>
+      <c r="E68" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="F68" s="47" t="s">
+        <v>269</v>
+      </c>
+      <c r="G68" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="H68" s="37" t="s">
+        <v>227</v>
+      </c>
+      <c r="I68" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="J68" s="37">
+        <v>4</v>
+      </c>
+      <c r="K68" s="37">
+        <f>J68*2</f>
+        <v>8</v>
+      </c>
+      <c r="L68" s="54"/>
+    </row>
+    <row r="69" spans="1:12" s="60" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A69" s="58"/>
+      <c r="B69" s="45">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+      <c r="C69" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="D69" s="47" t="s">
+        <v>304</v>
+      </c>
+      <c r="E69" s="47" t="s">
+        <v>107</v>
+      </c>
+      <c r="F69" s="47" t="s">
+        <v>269</v>
+      </c>
+      <c r="G69" s="47" t="s">
         <v>141</v>
       </c>
-      <c r="H66" s="47" t="s">
+      <c r="H69" s="47" t="s">
         <v>227</v>
       </c>
-      <c r="I66" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="J66" s="47">
-        <v>1</v>
-      </c>
-      <c r="K66" s="37">
+      <c r="I69" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="J69" s="47">
+        <v>1</v>
+      </c>
+      <c r="K69" s="37">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L66" s="55"/>
-    </row>
-    <row r="67" spans="1:12" s="61" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A67" s="59"/>
-      <c r="B67" s="44">
-        <f t="shared" si="2"/>
-        <v>58</v>
-      </c>
-      <c r="C67" s="48" t="s">
+      <c r="L69" s="54"/>
+    </row>
+    <row r="70" spans="1:12" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A70" s="58"/>
+      <c r="B70" s="44">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="C70" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="D67" s="37" t="s">
+      <c r="D70" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="E67" s="37" t="s">
+      <c r="E70" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="F67" s="37" t="s">
+      <c r="F70" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="G67" s="37" t="s">
+      <c r="G70" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="H67" s="37" t="s">
+      <c r="H70" s="37" t="s">
         <v>230</v>
       </c>
-      <c r="I67" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="J67" s="37">
-        <v>1</v>
-      </c>
-      <c r="K67" s="37">
+      <c r="I70" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="J70" s="37">
+        <v>1</v>
+      </c>
+      <c r="K70" s="37">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L67" s="55"/>
-    </row>
-    <row r="68" spans="1:12" s="61" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A68" s="59"/>
-      <c r="B68" s="44">
-        <f t="shared" si="2"/>
-        <v>59</v>
-      </c>
-      <c r="C68" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="D68" s="47" t="s">
-        <v>47</v>
-      </c>
-      <c r="E68" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="F68" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="G68" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="H68" s="37" t="s">
-        <v>232</v>
-      </c>
-      <c r="I68" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="J68" s="37">
-        <v>1</v>
-      </c>
-      <c r="K68" s="37">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="L68" s="55"/>
-    </row>
-    <row r="69" spans="1:12" s="61" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A69" s="59"/>
-      <c r="B69" s="44">
-        <f t="shared" si="2"/>
-        <v>60</v>
-      </c>
-      <c r="C69" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="D69" s="74" t="s">
-        <v>48</v>
-      </c>
-      <c r="E69" s="37" t="s">
-        <v>114</v>
-      </c>
-      <c r="F69" s="37" t="s">
-        <v>147</v>
-      </c>
-      <c r="G69" s="37" t="s">
-        <v>236</v>
-      </c>
-      <c r="H69" s="37" t="s">
-        <v>233</v>
-      </c>
-      <c r="I69" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="J69" s="37">
-        <v>1</v>
-      </c>
-      <c r="K69" s="37">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="L69" s="55"/>
-    </row>
-    <row r="70" spans="1:12" s="61" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A70" s="59"/>
-      <c r="B70" s="45">
-        <f t="shared" si="2"/>
-        <v>61</v>
-      </c>
-      <c r="C70" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="D70" s="75" t="s">
-        <v>49</v>
-      </c>
-      <c r="E70" s="47" t="s">
-        <v>115</v>
-      </c>
-      <c r="F70" s="47" t="s">
-        <v>148</v>
-      </c>
-      <c r="G70" s="47" t="s">
-        <v>201</v>
-      </c>
-      <c r="H70" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="I70" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="J70" s="47">
-        <v>1</v>
-      </c>
-      <c r="K70" s="37">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="L70" s="55"/>
-    </row>
-    <row r="71" spans="1:12" s="61" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A71" s="59"/>
+      <c r="L70" s="54"/>
+    </row>
+    <row r="71" spans="1:12" s="60" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A71" s="58"/>
       <c r="B71" s="44">
         <f t="shared" si="2"/>
         <v>62</v>
@@ -7164,143 +7225,143 @@
       <c r="C71" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="D71" s="75" t="s">
+      <c r="D71" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="E71" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="F71" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="G71" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="H71" s="37" t="s">
+        <v>232</v>
+      </c>
+      <c r="I71" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="J71" s="37">
+        <v>1</v>
+      </c>
+      <c r="K71" s="37">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L71" s="54"/>
+    </row>
+    <row r="72" spans="1:12" s="60" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A72" s="58"/>
+      <c r="B72" s="44">
+        <f t="shared" si="2"/>
+        <v>63</v>
+      </c>
+      <c r="C72" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="D72" s="62" t="s">
+        <v>48</v>
+      </c>
+      <c r="E72" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="F72" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="G72" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="H72" s="37" t="s">
+        <v>233</v>
+      </c>
+      <c r="I72" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="J72" s="37">
+        <v>1</v>
+      </c>
+      <c r="K72" s="37">
+        <f>J72*2</f>
+        <v>2</v>
+      </c>
+      <c r="L72" s="54"/>
+    </row>
+    <row r="73" spans="1:12" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A73" s="58"/>
+      <c r="B73" s="45">
+        <f t="shared" si="2"/>
+        <v>64</v>
+      </c>
+      <c r="C73" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="D73" s="63" t="s">
+        <v>49</v>
+      </c>
+      <c r="E73" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="F73" s="47" t="s">
+        <v>148</v>
+      </c>
+      <c r="G73" s="47" t="s">
+        <v>201</v>
+      </c>
+      <c r="H73" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="I73" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="J73" s="47">
+        <v>1</v>
+      </c>
+      <c r="K73" s="37">
+        <f>J73*2</f>
+        <v>2</v>
+      </c>
+      <c r="L73" s="54"/>
+    </row>
+    <row r="74" spans="1:12" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A74" s="58"/>
+      <c r="B74" s="44">
+        <f t="shared" si="2"/>
+        <v>65</v>
+      </c>
+      <c r="C74" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="D74" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="E71" s="37" t="s">
+      <c r="E74" s="37" t="s">
         <v>116</v>
       </c>
-      <c r="F71" s="37" t="s">
+      <c r="F74" s="37" t="s">
         <v>149</v>
       </c>
-      <c r="G71" s="37" t="s">
+      <c r="G74" s="37" t="s">
         <v>202</v>
       </c>
-      <c r="H71" s="37" t="s">
+      <c r="H74" s="37" t="s">
         <v>235</v>
       </c>
-      <c r="I71" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="J71" s="37">
-        <v>1</v>
-      </c>
-      <c r="K71" s="37">
-        <f t="shared" si="1"/>
+      <c r="I74" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="J74" s="37">
+        <v>1</v>
+      </c>
+      <c r="K74" s="37">
+        <f>J74*2</f>
         <v>2</v>
       </c>
-      <c r="L71" s="55"/>
-    </row>
-    <row r="72" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="59"/>
-      <c r="B72" s="45">
-        <f t="shared" si="2"/>
-        <v>63</v>
-      </c>
-      <c r="C72" s="49" t="s">
-        <v>24</v>
-      </c>
-      <c r="D72" s="75" t="s">
-        <v>51</v>
-      </c>
-      <c r="E72" s="47" t="s">
-        <v>117</v>
-      </c>
-      <c r="F72" s="47" t="s">
-        <v>150</v>
-      </c>
-      <c r="G72" s="47" t="s">
-        <v>203</v>
-      </c>
-      <c r="H72" s="47" t="s">
-        <v>212</v>
-      </c>
-      <c r="I72" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="J72" s="47">
-        <v>1</v>
-      </c>
-      <c r="K72" s="37">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="L72" s="55"/>
-    </row>
-    <row r="73" spans="1:12" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="59"/>
-      <c r="B73" s="45">
-        <f t="shared" si="2"/>
-        <v>64</v>
-      </c>
-      <c r="C73" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="D73" s="56" t="s">
-        <v>52</v>
-      </c>
-      <c r="E73" s="56" t="s">
-        <v>318</v>
-      </c>
-      <c r="F73" s="56" t="s">
-        <v>143</v>
-      </c>
-      <c r="G73" s="56" t="s">
-        <v>319</v>
-      </c>
-      <c r="H73" s="56" t="s">
-        <v>229</v>
-      </c>
-      <c r="I73" s="56" t="s">
-        <v>270</v>
-      </c>
-      <c r="J73" s="56">
-        <v>1</v>
-      </c>
-      <c r="K73" s="37">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="L73" s="55"/>
-    </row>
-    <row r="74" spans="1:12" s="61" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A74" s="59"/>
-      <c r="B74" s="45">
-        <f t="shared" si="2"/>
-        <v>65</v>
-      </c>
-      <c r="C74" s="49" t="s">
-        <v>24</v>
-      </c>
-      <c r="D74" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="E74" s="47" t="s">
-        <v>320</v>
-      </c>
-      <c r="F74" s="47" t="s">
-        <v>146</v>
-      </c>
-      <c r="G74" s="47" t="s">
-        <v>321</v>
-      </c>
-      <c r="H74" s="47" t="s">
-        <v>322</v>
-      </c>
-      <c r="I74" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="J74" s="47">
-        <v>1</v>
-      </c>
-      <c r="K74" s="37">
-        <f t="shared" ref="K74:K78" si="3">J74*2</f>
-        <v>2</v>
-      </c>
-      <c r="L74" s="55"/>
-    </row>
-    <row r="75" spans="1:12" s="61" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A75" s="59"/>
+      <c r="L74" s="54"/>
+    </row>
+    <row r="75" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="58"/>
       <c r="B75" s="45">
         <f t="shared" si="2"/>
         <v>66</v>
@@ -7308,92 +7369,92 @@
       <c r="C75" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="D75" s="37" t="s">
-        <v>54</v>
+      <c r="D75" s="63" t="s">
+        <v>51</v>
       </c>
       <c r="E75" s="47" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F75" s="47" t="s">
+        <v>150</v>
+      </c>
+      <c r="G75" s="47" t="s">
+        <v>203</v>
+      </c>
+      <c r="H75" s="47" t="s">
+        <v>212</v>
+      </c>
+      <c r="I75" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="J75" s="47">
+        <v>1</v>
+      </c>
+      <c r="K75" s="37">
+        <f>J75*2</f>
+        <v>2</v>
+      </c>
+      <c r="L75" s="54"/>
+    </row>
+    <row r="76" spans="1:12" s="60" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="58"/>
+      <c r="B76" s="45">
+        <f t="shared" si="2"/>
+        <v>67</v>
+      </c>
+      <c r="C76" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="D76" s="55" t="s">
+        <v>52</v>
+      </c>
+      <c r="E76" s="55" t="s">
+        <v>305</v>
+      </c>
+      <c r="F76" s="55" t="s">
+        <v>143</v>
+      </c>
+      <c r="G76" s="55" t="s">
+        <v>306</v>
+      </c>
+      <c r="H76" s="55" t="s">
+        <v>229</v>
+      </c>
+      <c r="I76" s="55" t="s">
+        <v>270</v>
+      </c>
+      <c r="J76" s="55">
+        <v>1</v>
+      </c>
+      <c r="K76" s="55">
+        <f t="shared" ref="K76:K79" si="3">J76*2</f>
+        <v>2</v>
+      </c>
+      <c r="L76" s="54"/>
+    </row>
+    <row r="77" spans="1:12" s="60" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A77" s="58"/>
+      <c r="B77" s="45">
+        <f t="shared" si="2"/>
+        <v>68</v>
+      </c>
+      <c r="C77" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="D77" s="47" t="s">
+        <v>53</v>
+      </c>
+      <c r="E77" s="47" t="s">
+        <v>307</v>
+      </c>
+      <c r="F77" s="47" t="s">
         <v>146</v>
       </c>
-      <c r="G75" s="47" t="s">
-        <v>200</v>
-      </c>
-      <c r="H75" s="47" t="s">
-        <v>231</v>
-      </c>
-      <c r="I75" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="J75" s="47">
-        <v>1</v>
-      </c>
-      <c r="K75" s="37">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="L75" s="55"/>
-    </row>
-    <row r="76" spans="1:12" s="61" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A76" s="59"/>
-      <c r="B76" s="45">
-        <f>ROW(B76) - ROW([1]Sheet1!$B$9)</f>
-        <v>67</v>
-      </c>
-      <c r="C76" s="49" t="s">
-        <v>24</v>
-      </c>
-      <c r="D76" s="47" t="s">
-        <v>323</v>
-      </c>
-      <c r="E76" s="47" t="s">
-        <v>324</v>
-      </c>
-      <c r="F76" s="47" t="s">
-        <v>325</v>
-      </c>
-      <c r="G76" s="47" t="s">
-        <v>326</v>
-      </c>
-      <c r="H76" s="47" t="s">
-        <v>327</v>
-      </c>
-      <c r="I76" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="J76" s="47">
-        <v>1</v>
-      </c>
-      <c r="K76" s="37">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="L76" s="55"/>
-    </row>
-    <row r="77" spans="1:12" s="61" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A77" s="59"/>
-      <c r="B77" s="45">
-        <f t="shared" si="2"/>
-        <v>68</v>
-      </c>
-      <c r="C77" s="49" t="s">
-        <v>328</v>
-      </c>
-      <c r="D77" s="37" t="s">
-        <v>329</v>
-      </c>
-      <c r="E77" s="47" t="s">
-        <v>330</v>
-      </c>
-      <c r="F77" s="47" t="s">
-        <v>270</v>
-      </c>
       <c r="G77" s="47" t="s">
-        <v>270</v>
+        <v>308</v>
       </c>
       <c r="H77" s="47" t="s">
-        <v>270</v>
+        <v>309</v>
       </c>
       <c r="I77" s="47" t="s">
         <v>270</v>
@@ -7405,31 +7466,31 @@
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="L77" s="55"/>
-    </row>
-    <row r="78" spans="1:12" s="61" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="59"/>
+      <c r="L77" s="54"/>
+    </row>
+    <row r="78" spans="1:12" s="60" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="58"/>
       <c r="B78" s="45">
         <f t="shared" si="2"/>
         <v>69</v>
       </c>
       <c r="C78" s="49" t="s">
-        <v>331</v>
+        <v>24</v>
       </c>
       <c r="D78" s="37" t="s">
-        <v>329</v>
+        <v>54</v>
       </c>
       <c r="E78" s="47" t="s">
-        <v>332</v>
+        <v>113</v>
       </c>
       <c r="F78" s="47" t="s">
-        <v>270</v>
+        <v>146</v>
       </c>
       <c r="G78" s="47" t="s">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H78" s="47" t="s">
-        <v>270</v>
+        <v>231</v>
       </c>
       <c r="I78" s="47" t="s">
         <v>270</v>
@@ -7441,35 +7502,70 @@
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="L78" s="55"/>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L78" s="54"/>
+    </row>
+    <row r="79" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
-      <c r="B79" s="62"/>
-      <c r="C79" s="63"/>
-      <c r="D79" s="64"/>
-      <c r="E79" s="65"/>
-      <c r="F79" s="66"/>
-      <c r="G79" s="67"/>
-      <c r="H79" s="66"/>
-      <c r="I79" s="66"/>
-      <c r="J79" s="66"/>
-      <c r="K79" s="66"/>
+      <c r="B79" s="45">
+        <f t="shared" si="2"/>
+        <v>70</v>
+      </c>
+      <c r="C79" s="49" t="s">
+        <v>310</v>
+      </c>
+      <c r="D79" s="37" t="s">
+        <v>311</v>
+      </c>
+      <c r="E79" s="47" t="s">
+        <v>312</v>
+      </c>
+      <c r="F79" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="G79" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="H79" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="I79" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="J79" s="47">
+        <v>1</v>
+      </c>
+      <c r="K79" s="37">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
       <c r="L79" s="68"/>
     </row>
     <row r="80" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
-      <c r="B80" s="25"/>
-      <c r="C80" s="36"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="10"/>
-      <c r="F80" s="10"/>
-      <c r="G80" s="10"/>
-      <c r="H80" s="10"/>
-      <c r="I80" s="69"/>
-      <c r="J80" s="69"/>
-      <c r="K80" s="69"/>
-      <c r="L80" s="51"/>
+      <c r="B80" s="38"/>
+      <c r="C80" s="39"/>
+      <c r="D80" s="40"/>
+      <c r="E80" s="41"/>
+      <c r="F80" s="42"/>
+      <c r="G80" s="43"/>
+      <c r="H80" s="42"/>
+      <c r="I80" s="61"/>
+      <c r="J80" s="61"/>
+      <c r="K80" s="61"/>
+      <c r="L80" s="50"/>
+    </row>
+    <row r="81" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="25"/>
+      <c r="C81" s="36"/>
+      <c r="D81" s="9"/>
+      <c r="E81" s="10"/>
+      <c r="F81" s="10"/>
+      <c r="G81" s="10"/>
+      <c r="H81" s="10"/>
+      <c r="I81" s="42"/>
+      <c r="J81" s="42"/>
+      <c r="K81" s="42"/>
+      <c r="L81" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="2">
